--- a/backend/POC/regulation_chunks.xlsx
+++ b/backend/POC/regulation_chunks.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B294\Downloads\cv10\backend\POC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AC4052-77CE-4233-B746-AEC5CACCCDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="277">
   <si>
     <t>chunk_id</t>
   </si>
@@ -34,30 +28,18 @@
     <t>contains_compliance_rule</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>no</t>
+    <t>document_name</t>
   </si>
   <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
   </si>
   <si>
-    <t>obligation</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
   </si>
   <si>
     <t>Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
   </si>
   <si>
-    <t>prohibition</t>
-  </si>
-  <si>
     <t>Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
   </si>
   <si>
@@ -100,19 +82,10 @@
     <t>Beneficial ownership verification should be conducted in a manner that is proportionate to the overall risk profile of the merchant, taking into account factors that the compliance team considers relevant at the time of assessment.</t>
   </si>
   <si>
-    <t>conditional</t>
-  </si>
-  <si>
     <t>Transaction monitoring alerts must be reviewed and actioned within a timeframe that is reasonable given the nature and severity of the alert, and in accordance with generally accepted industry practices.</t>
   </si>
   <si>
     <t>Staff supporting merchant accounts must receive adequate and up-to-date compliance training that is sufficient to enable them to perform their duties competently.</t>
-  </si>
-  <si>
-    <t>document_name</t>
-  </si>
-  <si>
-    <t>Synthetic Compliance Rules #1</t>
   </si>
   <si>
     <t>a:In circumstances where:
@@ -144,9 +117,6 @@
     <t>d:When we assess your claim, we will consider all relevant facts, the terms of your insurance policy and the law.</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>e:When we receive your Complaint, we will acknowledge that we have received it.</t>
   </si>
   <si>
@@ -165,26 +135,1071 @@
     <t>j:We will require our Employees and Distributors to receive appropriate education and training: a. to provide their services competently; b. to deal with you professionally; and c. about the Code.</t>
   </si>
   <si>
+    <t># 2023-COP_UPDATE_October_FINAL.pdf
+General Insurance Code of Practice
+Setting out standards of conduct for the general insurers who have adopted the Code and their Employees, Distributors and Service Suppliers.
+On behalf of the Board of the Insurance Council of Australia, I am pleased to present this updated version of the General Insurance Code of Practice 2020, which came into effect on 5 October 2021.
+The industry understands the vital role it plays in the community and the economy and the General Insurance Code of Practice continues to set a benchmark for self-regulation in the financial services sector. The 2020 Code was developed by the industry in consultation with multiple stakeholders and the result is the most customer-focused Code in its history, and one reflecting evolving community expectations. This includes a strong focus on supporting customers experiencing vulnerability.
+Most of the 2020 Code started on 1 July 2021, however some obligations, such as having a publicly available family violence policy, and the Supporting Customers Experiencing Vulnerability and Financial Hardship parts, took effect earlier.
+As the Code is a living document, some adjustments have now been made in this October 2021 version to align with ASIC’s new guidelines for complaints handling.
+For example, a new timeframe to resolve a complaint has been introduced reducing the time from 45 to 30 days.
+There is also a new commitment to promote improved awareness about the availability of Financial Hardship support on Code subscriber’s websites.
+The Code reflects the general insurance industry’s ongoing commitment to positive outcomes for consumers and its determination to provide best practice in conduct and customer service.
+I welcome the latest version of the 2020 Code and its ongoing improvements.
+Sue Houghton President Insurance Council of Australia 5 October 2021 President’s foreword
+Life can be unpredictable.
+Insurance can help protect you from life’s unpredictability. Some of the ways general insurance can protect you are:
+•  for loss or damage to your valuable possessions — such as your home or car, or even your Small Businesses and infrastructure; •  for your responsibility, or ‘liability’, to another person if you cause them loss or damage; and •  for loss you suffer from certain events such as travel cancellation and many types of natural disasters.
+By helping you to manage the financial impact of insured events, insurance can help reduce your stress.
+Although insurance is important in your personal and business affairs, insurance — and the insurance industry — underpin the Australian financial system. It does this by insuring risks for people and for the community and by helping them to rebuild and replace their assets after insured losses. Where a risk is not insured the burden of loss may have to be borne by the community. The insurance industry also contributes to improved risk management.
+To find out more about insurance, visit www.understandinsurance.com.au.</t>
+  </si>
+  <si>
+    <t>The Code The General Insurance Code of Practice (the Code) was introduced in 1994 by the Insurance Council of Australia as a voluntary Code. It has been regularly reviewed and updated.
+The Code is independently monitored and enforced by the Code Governance Committee.
+The Code has been developed through consultation with a range of stakeholders including consumer and industry representatives, the Code Governance Committee, the Australian Securities and Investments Commission and the Australian Financial Complaints Authority.
+The Code is intended to be a positive influence across all aspects of the general insurance industry including product disclosure, claims handling and investigations, relationships with people who are experiencing vulnerability, and reporting obligations.
+Meeting community needs, standards and expectations The general insurance industry is an integral part of an inclusive, thriving and adaptable community.
+The industry must always strive to meet the community’s evolving expectations for how it should support individuals and small businesses.
+The Code is a key way the general insurance industry makes sure it continues:
+•  to work towards this important goal; and •  to provide value to you and the whole community.
+General insurance in our society
+Our principles The principles that underpin the Code shape the way the general insurance industry behaves, treats people and approaches decision-making.
+We — the general insurance industry — will be inclusive by providing insurance designed to meet the diverse and changing needs of the whole community.
+We will provide value, transparency and fairness of products and services by:
+•  designing and selling insurance products and services that are of value to the community they are sold to; •  designing and selling insurance products and services in a clear, transparent and fair manner; and •  continually reviewing and improving insurance products and services offered to ensure they remain of value to the changing needs of the community.
+We will promote trust, integrity and respect by:
+•  meeting promises made to the community in a trusting environment; •  being open, fair and understanding, and acting with integrity, in our dealings with the community; •  being clear, transparent, fair and timely in our communications with the community; and •  treating the community with respect, dignity and sensitivity.
+We will provide accessibility and additional support by:
+•  being accessible to the community and making our processes simple and timely; and •  assisting members of the community who are in need of additional support.
+We will resolve any concerns and work to prevent future concerns by:
+•  listening and seeking to resolve concerns in an objective, truthful and timely manner; •  proactively resolving any concerns we may identify; and •  monitoring any concerns identified, and making changes to prevent similar future concerns when this is reasonable.</t>
+  </si>
+  <si>
+    <t>We will add value to the community by engaging with the government, consumers and other relevant stakeholders in building an inclusive, thriving and adaptable community.
+fairness of products and services trust integrity respect inclusive value transparency accessibility and additional support resolve any concerns and work to prevent future concerns
+President’s foreword General insurance in our society Part 1:
+Objectives of the Code Part 2:
+How the Code works What the Code means for you Who the Code applies to Code commencement Products the Code applies to Complying with the Code The Code and the law Part 3:
+Our obligation to you Part 4:
+Standards for us and our Distributors Conduct standards for us and our Employees and Distributors Education and training for our Employees and Distributors Dealing with concerns about our Employees or Distributors Concerns about other Australian Financial Service Licensees who sell our products 17 Part 5:
+Standards for our Service Suppliers Conduct standards for our Service Suppliers Appointing and monitoring Service Suppliers Dealing with concerns about our Service Suppliers Part 6:
+Buying insurance Pressure Selling Applying for or renewing insurance policies Sum insured calculators for home building policies Automatic renewal Premium comparison No Claims Discount Consumer Credit Insurance Part 7:
+Cancelling an insurance policy Part 8:
+Making a claim Before making a claim Making a claim Scope of works for a home building claim Issues with your claim Fast-tracking urgent claims Assessing your claim Using an External Expert, Loss Assessor, Loss Adjuster or Investigator Claim decision Cash settlements Claims for total loss Information we give you if we deny your claim or do not pay in full Changes to timeframes Use of repairers How we respond to Catastrophes Table of contents
+Part 9:
+Supporting customers experiencing vulnerability Internal policies and training Support measures Identification Using interpreters Mental health Part 10:
+Financial Hardship Individuals entitled to support Identifying people experiencing Financial Hardship Keeping you informed Assessing your request for Financial Hardship support Putting recovery on hold Making our decision If you are entitled to Financial Hardship support Releasing your debt If you are not entitled to Financial Hardship support Standards for collecting money Bankruptcy Part 11:
+Complaints Making a Complaint Handling your Complaint Decision about your Complaint Mistakes when handling your Complaint The Australian Financial Complaints Authority Complaint management by third parties Part 12:
+Your access to information Part 13:
+Enforcement, sanctions and compliance Reporting breaches The Code Governance Committee The responsibilities of the Code Governance Committee Imposing sanctions Types of sanctions Our compliance with the Code Part 14:
+Promoting, reviewing and improving the Code Promoting the Code Reviewing and improving the Code Part 15:</t>
+  </si>
+  <si>
+    <t>Claims investigation standards General investigation obligations Before any formal interview During the formal interview After the formal interview External Investigators only Surveillance Guide: Interview consent form Part 16:
+Definitions
+1.
+The objectives of the Code are:
+a. to commit us to high standards of service; b. to promote better, more informed relations between us and you; c. to maintain and promote trust and confidence in the general insurance industry; d. to provide fair and effective mechanisms for resolving Complaints you make about us; and e. to promote continuous improvement of the general insurance industry through education and training.
+2.
+We will pursue the above objectives of the Code with regard to the law and acknowledging that every contract of insurance is a contract based on the utmost good faith.
+Part 1:
+Objectives of the Code
+Part 2:
+How the Code works 3.
+Words and phrases that have a special meaning in the Code are listed with their meaning in part 16.
+What the Code means for you 4.
+We acknowledge that our customers, and our relationships with our customers, are the foundations of our business.
+5.
+If you have a concern about us, or about any aspect of your relationship with us, then you may:
+a. ask us to address the concern; b. make a Complaint to us through our Complaints process; and/or c. report your concerns to the Code Governance Committee.
+Who the Code applies to 6.
+The Code applies to all insurers who have adopted it. An organisation may adopt the Code if the organisation is a member of the Insurance Council of Australia; a general insurer; or approved by the Insurance Council of Australia. A list of Code subscribers is available at www.insurancecouncil.com.au.
+Code commencement 7.
+The Code takes effect on 5 October 2021.
+8.
+Once we have adopted the Code, then:
+a. all new policies and renewed policies we enter into are covered by the Code; b. all new claims we receive are covered by the relevant parts of the Code; and c. all new Complaints we receive are covered by the Code.
+9.
+If this Code applies, then any earlier version of the Code does not apply.
+Products the Code applies to</t>
+  </si>
+  <si>
+    <t>10.  The Code covers general insurance products with the exception of:
+a. Workers Compensation Insurance; b. Marine Insurance; c. Medical Indemnity Insurance; d. Motor Vehicle Injury Insurance; and e. Domestic Builders Insurance or Domestic Builders Warranty/Indemnity Insurance.
+11.
+Also, the Code does not cover:
+a. reinsurance; b. life insurance products issued by a life insurer; and c. health insurance products issued by a registered health insurer.</t>
+  </si>
+  <si>
+    <t>12.  The Code applies differently to Retail Insurance and Wholesale Insurance. The whole Code applies to Retail Insurance.
+The following parts of the Code do not apply to Wholesale Insurance:
+a. part 5 — Standards for our Service Suppliers b. part 6 — Buying insurance c. part 7 — Cancelling an insurance policy d. part 8 — Making a claim e. part 9 — Supporting customers experiencing vulnerability f. part 11 — Complaints (except in limited circumstances).</t>
+  </si>
+  <si>
+    <t>13.  If more than one insurer has insured a portion of the same risk under the same insurance policy (that is, under a co- insurance arrangement), then:
+a. if all of those insurers have adopted the Code, then the Code applies to that insurance policy; and b. if any of those insurers has not adopted the Code, then the Code does not apply to that insurance policy.
+Complying with the Code</t>
+  </si>
+  <si>
+    <t>14.  By adopting the Code, we enter voluntarily into a contract with the Insurance Council of Australia to comply with the Code.</t>
+  </si>
+  <si>
+    <t>15.  The Code does not create legal or other rights between us and any person or entity other than the Insurance Council of Australia.</t>
+  </si>
+  <si>
+    <t>16.  If we breach our obligations under the Code, the Code Governance Committee may impose sanctions on us as set out in part 13.</t>
+  </si>
+  <si>
+    <t>17.  We are in breach of the Code if our Employees, Distributors or Service Suppliers do not comply with the Code when they are acting on our behalf.
+Although our Distributors and Service Suppliers are not subscribers to this Code, they are accountable to us for complying with the relevant standards in the Code.
+The Code and the law</t>
+  </si>
+  <si>
+    <t>18.  The Code is designed to work with the many laws that cover our conduct and to deal with issues not dealt with in legislation. The Code does not limit your rights under law against us.</t>
+  </si>
+  <si>
+    <t>19.  Where there is an obligation under the Code in addition to a legal requirement, we will also comply with the Code, unless doing so would be in breach of the law.</t>
+  </si>
+  <si>
+    <t>20.  If there is any conflict or inconsistency between the Code and any Commonwealth, State or Territory law, then that law prevails.</t>
+  </si>
+  <si>
+    <t>21.  We, our Distributors and our Service Suppliers will be honest, efficient, fair, transparent and timely in our dealings with you.</t>
+  </si>
+  <si>
+    <t>22.  The Code sets out how we will meet this</t>
+  </si>
+  <si>
+    <t>obligation to you.
+Part 3:
+Our obligation to you
+Conduct standards for us and our Employees and Distributors</t>
+  </si>
+  <si>
+    <t>23.  We will have policies and procedures for our Employees and Distributors that require them to conduct sales appropriately and to prevent unacceptable sales practices.</t>
+  </si>
+  <si>
+    <t>24.  We will only allow our Employees and Distributors to provide services that match their expertise.</t>
+  </si>
+  <si>
+    <t>25.  When our Distributors are providing a service to you, they must tell you the service we have authorised them to provide and that they are acting on our behalf.</t>
+  </si>
+  <si>
+    <t>26.  If you make a Complaint to one of our Distributors, about either us or their conduct, then the Distributor must tell us about the Complaint within 2 Business Days. If your Complaint is about a Retail Insurance product, then your Complaint will be handled under the Code’s Complaints process.</t>
+  </si>
+  <si>
+    <t>27.  Our Distributors must notify us within 2 Business Days of any Code breaches by them when acting on our behalf.
+Education and training for our Employees and Distributors</t>
+  </si>
+  <si>
+    <t>28.  We will require our Employees and Distributors to receive appropriate education and training:
+a. to provide their services competently; b. to deal with you professionally; and c. about the Code.</t>
+  </si>
+  <si>
+    <t>29.  Our Employees’ education and training records will be kept for at least 7 years.
+We will make those records available to the Code Governance Committee at its request. We will require our Distributors to do the same.
+Dealing with concerns about our Employees or Distributors</t>
+  </si>
+  <si>
+    <t>30.  We will have policies and procedures in place to monitor the performance of our Employees and/or Distributors.</t>
+  </si>
+  <si>
+    <t>31.  We will investigate any concerns about the conduct of our Employees or Distributors that you raise with us, or that we are aware of. Where appropriate, we will address these concerns by — for example:
+a. requiring them to go through further training; or b. disciplinary action.</t>
+  </si>
+  <si>
+    <t>32.  If we identify that any of our Employees or Distributors have engaged in poor conduct in breach of our policies or procedures that has caused you material harm, then we will contact you to discuss an appropriate remedy. The remedy will depend on the circumstances and on what you agree to.
+For example, a remedy may include:
+a. us refunding any premiums paid; b. us paying interest on the refunded premium; c. us adjusting the cover the product provides; d. us correcting information provided to you; or e. us paying a claim.</t>
+  </si>
+  <si>
+    <t>33.  If you are not satisfied with our proposed remedy, then we will tell you how to make a Complaint.
+Part 4:
+Standards for us and our Distributors
+Concerns about other Australian Financial Service Licensees who sell our products</t>
+  </si>
+  <si>
+    <t>34.  If you have a concern about a person or organisation selling our product who is not one of our Distributors, you can contact us and we will let you know how you can have the matter addressed. You can also contact the Code Governance Committee.
+This part applies to Retail Insurance products only.
+Conduct standards for our Service Suppliers</t>
+  </si>
+  <si>
+    <t>35.  When our Service Suppliers are providing a service to you, they must tell you the service we have authorised them to provide and that they are acting on our behalf.</t>
+  </si>
+  <si>
+    <t>36.  If you make a Complaint to one of our Service Suppliers about either us or their conduct, then the Service Supplier will tell us about the Complaint within 2 Business Days. Your Complaint will be handled under the Code’s Complaints process.</t>
+  </si>
+  <si>
+    <t>37.  Our Service Suppliers must tell us within 2 Business Days about any breach of the Code that they are aware of when acting on our behalf.
+Appointing and monitoring Service Suppliers</t>
+  </si>
+  <si>
+    <t>38.  We will have measures in place to ensure that we appoint only suitable Service Suppliers. In particular, when we appoint a Service Supplier, they must:
+a. hold any licence the law requires; and b. reasonably satisfy us that they and their employees are qualified by education, training or experience (including but not limited to whether they hold membership with any relevant professional body) to provide the required service competently and to deal with you professionally.</t>
+  </si>
+  <si>
+    <t>39.  All contracts entered into with Service Suppliers after we have adopted the Code, must reflect the relevant standards of the Code.</t>
+  </si>
+  <si>
+    <t>40.  A Service Supplier must first get our approval before subcontracting any services they perform on our behalf.
+Dealing with concerns about our Service Suppliers</t>
+  </si>
+  <si>
+    <t>41.  If we are aware that our Service Suppliers’ performance does not meet the relevant standards of the Code, then we will address this — for example, by:
+a. cancelling our contract with the Service Supplier; or b. requiring them to go through further training.
+Part 5:
+Standards for our Service Suppliers
+This part applies to Retail Insurance products only.</t>
+  </si>
+  <si>
+    <t>42.  We will take reasonable steps to make sure that our communications are in plain language.</t>
+  </si>
+  <si>
+    <t>43.  We will have a publicly available policy on our approach to the development and distribution of our products for appropriate target markets. This policy will be published on our website.
+Pressure Selling</t>
+  </si>
+  <si>
+    <t>44.  Pressure Selling of our products is prohibited. We will make this clear to our Employees and Distributors.
+Applying for or renewing insurance policies</t>
+  </si>
+  <si>
+    <t>45.  If we are assessing your application for insurance, then we will ask for and rely on information and documents only if they are relevant to our decision.</t>
+  </si>
+  <si>
+    <t>46.  Where we identify, or you tell us, about a mistake in your application or in the information or documents we have relied on in assessing your application, we will immediately take action to correct it.</t>
+  </si>
+  <si>
+    <t>47.  If we cannot provide you with insurance, we will:
+a. give you our reasons for that decision; b. tell you about your right to ask us for the information we relied on when assessing your application — if you ask us for that information, then we will give it to you as set out in part 12 of the Code; c. refer you to either the Insurance Council of Australia or the National Insurance Brokers Association of Australia for information about your options for alternative insurance, or approaching another insurer or another broker; and d. give you information about our Complaints process if you tell us you are unhappy with our decision.
+Sum insured calculators for home building policies</t>
+  </si>
+  <si>
+    <t>48.  When you apply for or renew a home building insurance product, but not a strata insurance product, we will provide you with access to a calculator that is periodically reviewed and updated to enable you to estimate your sum insured.
+Automatic renewal</t>
+  </si>
+  <si>
+    <t>49.  If we are offering you an insurance product that can automatically renew, then, at the time of purchase and at each renewal we will:
+a. remind you about the automatic renewal process; b. remind you that you can opt-out of that process; and c. tell you to check the amount of your sum insured to see if your level of insurance cover is still appropriate for you.
+Premium comparison</t>
+  </si>
+  <si>
+    <t>50.  If we offer to renew any of the following products that you bought directly from us:
+a. home building; b. home contents; c. home building and home contents; d. motor vehicle — unless you have a fleet of vehicles or are a business or other organisation; then, in our renewal notice, we will give you a comparison between this year and last year’s premium and explain to you how it is calculated.
+Part 6:
+Buying insurance
+No Claims Discount</t>
+  </si>
+  <si>
+    <t>51.  If your insurance policy has a No Claims Discount, we must tell you how it works.
+A No Claims Discount is sometimes called a ‘No Claims Bonus’ or a ‘No Claims Entitlement’.
+Consumer Credit Insurance</t>
+  </si>
+  <si>
+    <t>52.  We will not sell you a Consumer Credit Insurance product during the deferred sales period.</t>
+  </si>
+  <si>
+    <t>53.  If we, or any intermediary acting on our behalf, offer you Consumer Credit Insurance for credit cards, home loans or personal loans, then we will take reasonable steps to ensure that:
+a. you are given clear information, before the deferred sales period starts, about the cost of the Consumer Credit Insurance, the options for payment, how long it lasts and its key exclusions and limits; b. you are informed that purchasing the Consumer Credit Insurance has no bearing on whether your application for a credit card, personal or home loan will be approved; and c. no binding offer of Consumer Credit Insurance can be made to you until the end of the deferred sales period.</t>
+  </si>
+  <si>
+    <t>54.  The deferred sales period is 4 days, starting on the day after you are informed that your credit card, home loan or personal loan is approved.
+This part applies to Retail Insurance products only.</t>
+  </si>
+  <si>
+    <t>55.  Your insurance policy may allow you to cancel it and obtain a refund. If you are entitled to a refund and you cancel your policy, then we will return the amount within 15 Business Days. However, if you arranged your insurance through an insurance broker, then different arrangements will apply — you will need to ask your broker about those arrangements.</t>
+  </si>
+  <si>
+    <t>56.  If you have an Instalment Policy and we have not received an instalment payment, then we will send you a notice in writing regarding your non-payment at least 14 Calendar Days before any cancellation by us for non-payment.</t>
+  </si>
+  <si>
+    <t>57.  If after sending the notice under paragraph 56 we do not receive the instalment payment for the Instalment Policy, then we will send you a second notice in writing either:
+a. before cancellation, informing you that your Instalment Policy is being cancelled for non-payment; or b. within 14 Calendar Days after cancellation by us, confirming our cancellation of your Instalment Policy.
+Part 7:
+Cancelling an insurance policy
+This part applies to Retail Insurance products only.
+Before making a claim</t>
+  </si>
+  <si>
+    <t>58.  You can ask us if your insurance policy covers a particular loss before you actually make a claim. When we answer your question, we will not discourage you from making a claim and we will tell you that if you make a claim, we will fully assess whether your loss is covered.
+Making a claim</t>
+  </si>
+  <si>
+    <t>59.  If you make a claim, then we will tell you:
+a. about our claims process; b. about any excess amounts you have to cover or pay in relation to your claim; c. about any waiting or no cover periods that need to finish before we start paying you under the policy; and d. how to contact us regarding your claim.</t>
+  </si>
+  <si>
+    <t>60.  If we are contacted by an uninsured person who wishes to make a claim against one of our customers, then we will tell them about our claims process and what is required for us to start a claim. If we have accepted a claim under our insured’s motor vehicle policy, then we will tell them:
+a. about the next steps in the claims process; b. about our Complaints process; and c. who to contact to find out about any claim they make, and their contact details.
+Scope of works for a home building claim</t>
+  </si>
+  <si>
+    <t>61.  If a scope of works is needed for a home building claim, we will provide you with information to help you understand how it works, its purpose and the process involved.
+Issues with your claim</t>
+  </si>
+  <si>
+    <t>62.  If we identify, or you tell us about a mistake we make in handling your claim, then we will immediately take action to correct the mistake.</t>
+  </si>
+  <si>
+    <t>63.  If you have a Complaint about anything to do with how we handle your claim, then you may make a Complaint to us through our Complaints process.
+Fast-tracking urgent claims</t>
+  </si>
+  <si>
+    <t>64.  Where the event (for example, a natural disaster) that caused you to make a claim under your policy also caused you to be in urgent financial need of the benefits you are entitled to under that policy, then we will do either or both of the following:
+a. fast-track both our assessment of your claim and the process we follow to make a decision about your claim; b. pay you an advance amount to help ease your urgent financial need — we will do this within 5 Business Days after you demonstrate your urgent financial need.</t>
+  </si>
+  <si>
+    <t>65.  See part 10 of the Code to read more about applying for Financial Hardship support.</t>
+  </si>
+  <si>
+    <t>66.  If you are not happy with our response to your request about urgent financial need, then we will tell you about our Complaints process.
+Assessing your claim</t>
+  </si>
+  <si>
+    <t>67.  When we are assessing your claim, we will only ask for and rely on information that is relevant to our decision. If we ask you for information, then we will tell you why we need it.
+Part 8:
+Making a claim</t>
+  </si>
+  <si>
+    <t>68.  If you make a claim and we need further information or assessment, then within 10 Business Days of receiving your claim we will:
+a. tell you any information we need to make a decision on your claim. We will use our best endeavours to do that in one request; b. if necessary, appoint a Loss Assessor or Loss Adjuster to assess your claim; and c. provide our estimate of the likely timeframe and process for us to make a decision about your claim.</t>
+  </si>
+  <si>
+    <t>69.  When we assess your claim, we will consider all relevant facts, the terms of your insurance policy and the law.</t>
+  </si>
+  <si>
+    <t>70.  We will tell you about the progress of your claim at least every 20 Business Days.</t>
+  </si>
+  <si>
+    <t>71.  We will respond to your routine enquiries about your claim’s progress within 10 Business Days.
+Using an External Expert, Loss Assessor, Loss Adjuster or Investigator</t>
+  </si>
+  <si>
+    <t>72.  If we appoint a Loss Assessor or Loss Adjuster, then within 5 Business Days we will tell you that we have appointed them and what their role is. An appointed loss assessor or loss adjustor may be an Employee.</t>
+  </si>
+  <si>
+    <t>73.  If we appoint an Investigator or Employee to investigate your claim, then within 5 Business Days we will tell you that we have appointed them and what their role is. When we appoint an Investigator or Employee to investigate your claim, then the investigation process will comply with the Claims Investigation Standards (see part 15).</t>
+  </si>
+  <si>
+    <t>74.  If we engage an External Expert to provide us with a report that we need to assess your claim, then we will ask them to report to us within 12 weeks of us engaging them. If the External Expert does not meet that timeframe, we will tell you and keep you informed of our progress in obtaining the report.</t>
+  </si>
+  <si>
+    <t>75.  We will engage an External Expert only if we believe they have the appropriate expertise to provide the opinion we ask them for and that they comply with the rules and regulations relevant to their area of expertise.
+Claim decision</t>
+  </si>
+  <si>
+    <t>76.  Once we have all relevant information and have completed all enquiries, we will decide whether to accept or deny your claim and tell you of our decision within 10 Business Days.</t>
+  </si>
+  <si>
+    <t>77.  Our decision will be made within 4 months of receiving your claim, unless paragraph 78 applies. If we do not make a decision within that time, we will tell you in writing about our Complaints process.</t>
+  </si>
+  <si>
+    <t>78.  In circumstances where:
+a. your claim arises from an Extraordinary Catastrophe; b. your claim is fraudulent, or we reasonably suspect it is fraudulent; c. you do not respond to our reasonable inquiries or to our requests for documents or information about your claim; d. we have difficulty communicating with you about your claim due to circumstances beyond our control; or e. you request a delay in the claims process; then within 12 months of receiving your claim we will tell you our decision in writing. If we cannot make a decision within 12 months, we will tell you in writing about our Complaints process.
+Cash settlements</t>
+  </si>
+  <si>
+    <t>79.  If we offer a cash settlement under a home building policy, we will provide you with information to help you understand how they work and how decisions are made on cash settlements.
+Claims for total loss</t>
+  </si>
+  <si>
+    <t>80.  When you have suffered a total loss, we and our Service Suppliers will treat your claim with sensitivity. If we have accepted your claim for a total loss under your home building and home contents insurance policy and you are
+unable to provide proof of ownership for the relevant insured property because it was lost in or damaged by the insured event (and we believe your ownership is clear) we will not:
+a. require you to provide proof of ownership; or b. require a list of insured property that was lost or damaged.
+Information we give you if we deny your claim or do not pay in full</t>
+  </si>
+  <si>
+    <t>81.  If we deny your claim, or do not pay it in full, then we will tell you, in writing:
+a. the aspects of your claim that we do not accept; b. the reasons for our decision; c. that you have the right to ask us for the information about you that we relied on when assessing your claim; d. that you have the right to ask us for copies of any Service Suppliers’ or External Experts’ reports that we relied on; and e. about our Complaints process.</t>
+  </si>
+  <si>
+    <t>82.  If you ask for information or for copies of any Service Suppliers’ or External Experts’ reports that we relied on, then we will give you that information or report within 10 Business Days, as set out in part 12 of the Code.
+Changes to timeframes</t>
+  </si>
+  <si>
+    <t>83.  If any of the timeframes in this part are not practical due, for example, to the complex nature of your claim, we will agree a reasonable alternative timetable with you. If we cannot reach an agreement on an alternative timetable, we will provide details of our Complaints process.</t>
+  </si>
+  <si>
+    <t>84.  We must comply with the timeframes in this part of the Code, unless any of the following apply:
+a. we have complied with an alternative timetable to which you agreed; b. our conduct, and the actual timeframe, were reasonable in all the circumstances; c. the reason we did not comply with the timeframe was that a report from an External Expert was delayed, even though we used our best endeavours to obtain the report in time.</t>
+  </si>
+  <si>
+    <t>85.  The standards in this part of the Code do not apply to your claim if you have commenced any proceedings against us about your claim in any court, tribunal or under any other dispute handling process, other than through the Australian Financial Complaints Authority.
+Use of repairers</t>
+  </si>
+  <si>
+    <t>86.  If we have selected and directly authorised a repairer to repair your damaged property, then we will accept responsibility for the quality of their work and the materials they use. Complaints about the repairer’s conduct, timeliness, quality of work or the materials they use will be handled under our Complaints process.</t>
+  </si>
+  <si>
+    <t>87.  If we have selected and directly authorised a repairer and we are satisfied that the repair requires rectification and because of that you need a hire car or accommodation over and above what we would provide to you in your policy, then we will arrange these for you and cover the reasonable costs.
+How we respond to Catastrophes</t>
+  </si>
+  <si>
+    <t>88.  We will respond to Catastrophes efficiently, professionally, practically and compassionately.</t>
+  </si>
+  <si>
+    <t>89.  We will co-operate and work with the Insurance Council of Australia on industry coordination and communications under the Insurance Council of Australia’s industry Catastrophe coordination arrangements.</t>
+  </si>
+  <si>
+    <t>90.  If you have a property claim resulting from a Catastrophe and we have finalised your claim within 1 month after the Catastrophe event causing your loss, you can request a review of your claim if you think that assessment of your loss was not complete or accurate, even though you may have signed a release. We will give you 12 months from the date of finalisation of your claim to ask for a review of your claim. We will inform you in writing about this entitlement and our Complaints process when we finalise your claim.
+Part 9:
+Supporting customers experiencing vulnerability This part applies to Retail Insurance products only.</t>
+  </si>
+  <si>
+    <t>91.  We are committed to taking extra care with customers who experience vulnerability.
+We recognise that a person’s vulnerabilities can give rise to unique needs, and that their needs can change over time and in response to particular situations.</t>
+  </si>
+  <si>
+    <t>92.  A person’s vulnerability may be due to a range of factors such as:
+a. age; b. disability; c. mental health conditions; d. physical health conditions; e. family violence; f. language barriers; g. literacy barriers; h. cultural background; i.  Aboriginal or Torres Strait Islander status; j.  remote location; or k. financial distress.</t>
+  </si>
+  <si>
+    <t>93.  We encourage you to tell us about your vulnerability so that we can work with you to arrange support — otherwise, there is a risk that we may not find out about it.</t>
+  </si>
+  <si>
+    <t>94.  If you are experiencing Financial Hardship, see part 10 of the Code about the support we can provide to you.
+Internal policies and training</t>
+  </si>
+  <si>
+    <t>95.  We will have a publicly available policy about how we will support you if you are affected by family violence. This policy will be published on our website.</t>
+  </si>
+  <si>
+    <t>96.  We will have internal policies and training appropriate to our Employees’ roles to help them:
+a. understand if you may be vulnerable; b. decide about how best, and to what extent, we can support you; c. take account of your particular needs or vulnerability; and d. engage with you with sensitivity, dignity, respect and compassion — this may include arranging additional support, for example referring you to people, or services, with specialist training and experience.
+Support measures</t>
+  </si>
+  <si>
+    <t>97.  If you tell us, or we identify, that due to a vulnerability you need additional support or assistance, we will work with you and try to find a suitable, sensitive and compassionate way for us to proceed.
+We will do this as early as practicable and we will protect your right to privacy.</t>
+  </si>
+  <si>
+    <t>98.  If you tell us, or we identify, that you need additional support from someone else (for example, a lawyer, consumer representative, interpreter or friend), then we will recognise this and allow for it in all reasonable ways.
+We will try to make sure our processes are flexible enough to recognise the authority of your support person.</t>
+  </si>
+  <si>
+    <t>99.  Additional support may include making it easier for you to communicate with us, referring you to a financial counsellor or an appropriate community support service.
+Identification</t>
+  </si>
+  <si>
+    <t>100. If you need support to meet identification requirements, then we will take reasonable measures to support you — particularly if you are from an Aboriginal or Torres Strait Islander community or a non-English speaking background. Our approach to supporting you with verification and identification will be flexible.
+Using interpreters</t>
+  </si>
+  <si>
+    <t>101.  Where practicable, we will provide access to an interpreter if you ask us to, or if we need an interpreter to communicate effectively with you. We will record if an interpreter is used or if there are reasons we are unable to arrange one.</t>
+  </si>
+  <si>
+    <t>102. We will arrange relevant training for our Employees who are likely to be involved in communications requiring an interpreter.</t>
+  </si>
+  <si>
+    <t>103. On our website there will be an easy-to- find link to:
+a. information on interpreting services; b. teletypewriter services (TTYs); c. any information on our products that we have translated into other languages; and d. any other relevant information for people with language barriers.
+Mental health</t>
+  </si>
+  <si>
+    <t>104. When developing our internal processes and procedures we will take into account those who have a past or current mental health condition by doing the following:
+a. at a minimum, we will design and sell our products and apply their terms in compliance with the requirements of the Disability Discrimination Act 1992 and/or any relevant State or Territory anti-discrimination requirements; b. we will treat people with any past or current mental health condition fairly; c. we will only ask relevant questions when deciding whether to provide cover for a pre-existing mental health condition; d.  if we cannot provide you with cover for that condition we will tell you about your right to ask us for the information relied on when assessing your application. If you ask for that information, then we will give it to you as set out in part 12 of the Code.
+Individuals entitled to support</t>
+  </si>
+  <si>
+    <t>105. We will have information about applying for Financial Hardship support on our website. The information will set out the types of support options that may be available, and how you can access Financial Hardship support.</t>
+  </si>
+  <si>
+    <t>106. You have a right to ask us to fast-track a claim if you have an urgent financial need.
+See paragraph 64.</t>
+  </si>
+  <si>
+    <t>107.  You may be entitled to support because you are suffering Financial Hardship if you are:
+a. an individual Insured or a Third Party Beneficiary who owes us money — including an excess — under an insurance policy we have issued; or b. an individual and we are seeking to recover money from you because we believe you caused damage or loss to either an Insured, or a Third Party Beneficiary who we cover under an insurance policy.</t>
+  </si>
+  <si>
+    <t>108. The support that we provide does not include support with paying the premiums under an insurance policy we have issued.
+Identifying people experiencing Financial Hardship</t>
+  </si>
+  <si>
+    <t>109. We will have internal policies and training appropriate to our Employees’ roles to help them to identify if you are experiencing Financial Hardship and decide how they may be able to provide support to you.</t>
+  </si>
+  <si>
+    <t>110.  We encourage you or your representative to tell us about your Financial Hardship so that we can work with you to discuss your situation and the options available to support you — otherwise there is a risk that we may not find out about it.</t>
+  </si>
+  <si>
+    <t>111.  If you tell us, or we identify, that you are experiencing Financial Hardship, we will give you:
+a. details about how to apply for Financial Hardship support; and b. if appropriate, contact details for the National Debt Helpline: 1800 007 007.
+Keeping you informed</t>
+  </si>
+  <si>
+    <t>112.  We will communicate with you about your application and where possible, we will use your preferred method of communication.</t>
+  </si>
+  <si>
+    <t>113.  If we know that you have nominated a representative, then we will keep that person updated about your request for Financial Hardship support, unless you tell us not to.
+Assessing your request for Financial Hardship support</t>
+  </si>
+  <si>
+    <t>114.  When we are assessing your request for Financial Hardship support, we will consider all reasonable evidence — for example:
+a. evidence of serious illness that prevents you from earning income; b. evidence of a disability, including a disability caused by mental illness; c. if you are a Centrelink client, your Centrelink statements; and d. evidence of your unemployment.</t>
+  </si>
+  <si>
+    <t>115.  We will request information from you only if it is reasonably necessary for us to assess your application for Financial Hardship support.</t>
+  </si>
+  <si>
+    <t>116.  If, after we receive your application for Financial Hardship support, we need more information from you before we can make our decision, then we will:
+a. tell you the information we need as early as possible; and b. be specific about the information we need.</t>
+  </si>
+  <si>
+    <t>117.  You have 21 Calendar Days from the date of our request under paragraph 116 to Part 10:
+Financial Hardship
+provide that information to us, unless we have agreed to a different timeframe.
+Putting recovery on hold</t>
+  </si>
+  <si>
+    <t>118.  If we are taking action to recover an amount from you, we will put that action on hold if we identify that you are experiencing Financial Hardship, or if you ask us for Financial Hardship support in relation to that amount.</t>
+  </si>
+  <si>
+    <t>119.  When we put the action on hold, we will contact any Collection Agent or solicitor that we have appointed and tell them the action is on hold.</t>
+  </si>
+  <si>
+    <t>120. The action will stay on hold until we have assessed your application for Financial Hardship and notified you of our decision about it.
+Making our decision</t>
+  </si>
+  <si>
+    <t>121.  We will tell you in writing of our decision about whether to give you Financial Hardship support within 21 Calendar Days after we receive your application, unless we have asked you to provide us with more information.</t>
+  </si>
+  <si>
+    <t>122. If we do ask you for more information under paragraph 116 and:
+a. you provide all information we requested, then within 21 Calendar Days of receiving it we will tell you in writing, our decision about whether to give you Financial Hardship support; or b. you do not provide all information we requested within 21 Calendar Days (or by a later date we agree to), then within 7 Calendar Days of that deadline passing, we will tell you in writing, our decision about whether to give you Financial Hardship support.
+If you are entitled to Financial Hardship support</t>
+  </si>
+  <si>
+    <t>123. If we decide you are entitled to Financial Hardship support, then we will work with you to implement an arrangement that could include any one or more of the following:
+a. delaying the date on which the payment must be made; b. paying us in instalments — we will not refuse a reasonable request from you to pay the amount you owe in instalments; c. paying a reduced lump sum amount; d. delaying one or more instalment payments for an agreed period; e. deducting the excess from the claim amount we pay you; f. waiving cancellation fees.</t>
+  </si>
+  <si>
+    <t>124. We will confirm the agreed arrangement with you. Where possible this will be in your preferred method of communication.</t>
+  </si>
+  <si>
+    <t>125. If we agree you are entitled to Financial Hardship support, but we are unable to agree about how you can be supported, then we will tell you in writing, about our Complaints process.
+Releasing your debt</t>
+  </si>
+  <si>
+    <t>126. If we decide you are entitled to Financial Hardship support, then you may ask us to release, discharge, or waive a debt or obligation. However, you are not automatically entitled to this.</t>
+  </si>
+  <si>
+    <t>127.  If we agree to release, discharge or waive a debt or obligation, then we will confirm this with you in writing.</t>
+  </si>
+  <si>
+    <t>128. You can ask us to notify any financial institution with an interest in your insurance policy that you are entitled to Financial Hardship support and, if applicable, that we have released, discharged or waived a debt or obligation.
+If you ask us to do this, then we will tell them about this in writing.
+If you are not entitled to Financial Hardship support</t>
+  </si>
+  <si>
+    <t>129. If we decide that you are not entitled to Financial Hardship support, we will tell you the reasons for our decision and about our Complaints process. Where possible, we will tell you this in your preferred method of communication.</t>
+  </si>
+  <si>
+    <t>130. If your circumstances change, then you may re-apply for Financial Hardship support in relation to the amount you owe.
+However, for any further application you make, it will be at our discretion whether we again put any recovery action on hold.
+Standards for collecting money</t>
+  </si>
+  <si>
+    <t>131.  We, as well as any Collection Agent or solicitor collecting money for us, will comply with the Debt collection guideline:
+for collectors and creditors published by the Australian Competition and Consumer Commission and the Australian Securities and Investments Commission.</t>
+  </si>
+  <si>
+    <t>132. We, as well as any Collection Agent or solicitor collecting money for us, are required to:
+a. understand the Financial Hardship requirements in the Code; and b. receive training to help identify whether you might need Financial Hardship support.</t>
+  </si>
+  <si>
+    <t>133. When we, our Collection Agent or solicitor, first communicates with you about any money owed, then we will ensure that this communication will provide you with information to show that the amount we are seeking to recover from you is fair and reasonable. This may include:
+a. information on the relevant loss and/or damage and the claim; b. the actual cost of completed repairs; and c. the evidence we relied on when we calculated the amount.</t>
+  </si>
+  <si>
+    <t>134. This communication will also include:
+a. information about our Financial Hardship process; and b. contact details to enable you to contact us to discuss Financial Hardship support or if you have any questions.</t>
+  </si>
+  <si>
+    <t>135. If our Collection Agent or solicitor communicates with you about money owed, then that communication will identify us as the insurer that they are acting on behalf of and will specify the nature of our claim against you.</t>
+  </si>
+  <si>
+    <t>136. If you tell our Collection Agent or solicitor that you are experiencing Financial Hardship, then they must notify us and give you information in writing about our Financial Hardship process.
+Bankruptcy</t>
+  </si>
+  <si>
+    <t>137.  If you tell us that you intend to declare bankruptcy, then we will work with you (or your representative) to agree on the amount owed. We will also give you written confirmation of that amount for the purposes of your declaration of bankruptcy.</t>
+  </si>
+  <si>
+    <t>138. If we cannot agree on an amount, then we will provide details of our Complaints process in writing.
+Part 11:
+Complaints This part applies to Retail Insurance products.
+In addition, it is available to an uninsured person making a claim against a customer who we insure under a Retail Insurance policy (see paragraph 60).
+This part also applies to Wholesale Insurance products where you are entitled to Financial Hardship support under paragraph 107(b).
+Making a Complaint</t>
+  </si>
+  <si>
+    <t>139. You may complain to us about any aspect of your relationship with us.</t>
+  </si>
+  <si>
+    <t>140. We will make readily available information about:
+a. your right to make a Complaint; b. our internal processes for dealing with Complaints; and c. our external dispute resolution provider.
+This will be published on our website, other digital platforms and in our relevant written communications.</t>
+  </si>
+  <si>
+    <t>141.  Our Complaints process will comply with the Australian Securities and Investments Commission’s guidelines.
+Handling your Complaint</t>
+  </si>
+  <si>
+    <t>142. When we receive your Complaint, we will acknowledge that we have received it.</t>
+  </si>
+  <si>
+    <t>143. We will tell you the name and relevant contact details of the person assigned to liaise with you about your Complaint.</t>
+  </si>
+  <si>
+    <t>144. Your Complaint will be handled by a person with appropriate authority, knowledge or experience. This will not be the person whose decision or conduct is what your Complaint is about.</t>
+  </si>
+  <si>
+    <t>145. When we are considering your Complaint, we will only ask for, and rely on, information that is relevant to our decision.</t>
+  </si>
+  <si>
+    <t>146. We will keep you informed about the progress of your Complaint at least every 10 Business Days, unless it is resolved earlier or you agree to a different timeframe.
+Decision about your Complaint</t>
+  </si>
+  <si>
+    <t>147.  We will make a decision about your Complaint within 30 Calendar Days. If we cannot make our decision within this timeframe, then before this deadline passes we will tell you, in writing, the reasons for the delay and about your right to take your Complaint to the Australian Financial Complaints Authority, and its contact details.</t>
+  </si>
+  <si>
+    <t>148. When we have made a final decision about your Complaint we will respond to you in writing, unless paragraph 150 applies.</t>
+  </si>
+  <si>
+    <t>149. Our written response to you will include the reasons for our decision and inform you of your right to take your Complaint to the Australian Financial Complaints Authority if you are not satisfied with our decision. We will provide you with its contact details and the timeframe in which you are able to complain to it.</t>
+  </si>
+  <si>
+    <t>150. We will provide you with a written response where your Complaint is about Financial Hardship, a declined claim, the value of a claim or you have requested a written response. Otherwise, a written response may not be provided where, within 5 business days, we have been able to resolve your Complaint to your satisfaction, or we have given you an explanation and/or an apology and can take no further action to reasonably address your Complaint.</t>
+  </si>
+  <si>
+    <t>151.  We must give you the information that we relied on when making a decision about your Complaint within 10 Business Days of you asking us for that information. We will give you the information as set out in part 12 of the Code.
+Mistakes when handling your Complaint</t>
+  </si>
+  <si>
+    <t>152. If it is identified that we have made a mistake when handling your Complaint, then we will take action to correct the mistake.
+The Australian Financial Complaints Authority</t>
+  </si>
+  <si>
+    <t>153. We are part of an independent external dispute resolution scheme administered by the Australian Financial Complaints Authority. The scheme is for customers and third parties as allowed under its Rules.</t>
+  </si>
+  <si>
+    <t>154. You can take your Complaint to the Australian Financial Complaints Authority at any time and if we do not resolve your Complaint within 30 Calendar Days after we first received your Complaint.</t>
+  </si>
+  <si>
+    <t>155. Under the Australian Financial Complaints Authority’s Rules, your Complaint may be referred back to us if it has not gone through our Complaints process.</t>
+  </si>
+  <si>
+    <t>156. The Australian Financial Complaints Authority’s decisions are binding on us in the way set out in its Rules.</t>
+  </si>
+  <si>
+    <t>157.  If the Australian Financial Complaints Authority tells you that under its Rules it cannot assist you or consider your dispute, then you can seek independent legal advice. You can also access any other external dispute resolution or other options that may be available to you.
+Complaint management by third parties</t>
+  </si>
+  <si>
+    <t>158. We may authorise another person to act on our behalf to receive and handle Complaints about our products and services.</t>
+  </si>
+  <si>
+    <t>159. Where we authorise another person to receive and handle Complaints under paragraph 158, then:
+a. that person must notify us of Complaints made to them; b. they must handle Complaints in accordance with the requirements as set out in this part of the Code; c. any breach of this part of the Code by them is a breach of the Code by us; d. we will have processes in place to monitor their handling of Complaints and take reasonable steps to ensure that they are meeting the requirements as specified in this part of the Code.</t>
+  </si>
+  <si>
+    <t>160. We comply with the Principles of the Privacy Act 1988 and/or any relevant State or Territory requirements when we collect, store, use, disclose and destroy personal information about you.</t>
+  </si>
+  <si>
+    <t>161.  At your request, and subject to paragraph 163, we must give you — free of charge, access to any information that we relied on in assessing your application for insurance cover, or in handling your claim, or in responding to your Complaint. We must give you this information within 30 Calendar Days unless paragraph 82 or 151 applies.</t>
+  </si>
+  <si>
+    <t>162. The information you may access includes:
+a. documents and information we relied on to deny your claim; b. copies of your product disclosure statement and insurance; c. copies of any reports from Service Suppliers or External Experts that we relied on; and d. copies of any recordings and/or transcripts of any interaction we had with you that we relied on.</t>
+  </si>
+  <si>
+    <t>163. If we refuse to give you access to information, we will not do so unreasonably, and we will tell you our reasons for doing so and about our Complaints process. We may refuse to give you access to information in the following circumstances:
+a. where a law — for example, the Privacy Act 1988 — says we do not have to; b. in the case of a claim where the claim is being or has been investigated, and giving access would have an unreasonable impact on the privacy of other individuals or government agencies; or c. if doing so may be prejudicial to us in relation to a Complaint or a dispute about your insurance cover or your claim — however, even in this circumstance we must give you access to any External Experts’ reports we relied on.
+Part 12:
+Your access to information
+Reporting breaches</t>
+  </si>
+  <si>
+    <t>164. Anyone can report alleged breaches of the Code to the Code Governance Committee at any time.
+The Code Governance Committee</t>
+  </si>
+  <si>
+    <t>165. The Code is monitored and enforced by the Code Governance Committee which is an independent body. The Code Governance Committee is made up of:
+a. a consumer representative; b. an industry representative; and c. an independent chair.</t>
+  </si>
+  <si>
+    <t>166. The Code Governance Committee’s constitution, functions and powers are set out in its Charter.</t>
+  </si>
+  <si>
+    <t>167. The Code Governance Committee may outsource to an appropriate service provider any of the following responsibilities:
+a. monitoring and enforcing compliance with the Code; b. annual reporting; c. the responsibilities under paragraphs 168 and 169.
+The responsibilities of the Code Governance Committee</t>
+  </si>
+  <si>
+    <t>168. The Code Governance Committee is responsible for:
+a. providing stewardship of the Code by helping the general insurance industry understand and comply with the Code; b. identifying areas for improvement of insurance practices; c. liaising with the Insurance Council of Australia on relevant matters; d. providing quarterly reports to the Board of the Insurance Council of Australia; e. publishing an annual public report containing aggregate industry data and consolidated analysis on Code compliance.</t>
+  </si>
+  <si>
+    <t>169. The Code Governance Committee is also responsible for monitoring and enforcing compliance with the Code through:
+a. investigations, analysis of data, analysis of evidence and stakeholder engagement; b. receiving, investigating and making decisions about alleged breaches and giving us the opportunity to respond to any allegations that we have breached the Code; c. considering whether it is more appropriate for the Australian Securities and Investments Commission or another enforcement agency to investigate an alleged breach of the Code; d. agreeing with us on any corrective measures to implement within an agreed timeframe; e. imposing sanctions; and f. publishing breach decisions on a de-identified basis.
+Imposing sanctions</t>
+  </si>
+  <si>
+    <t>170. The Code Governance Committee may impose sanctions on us for a breach of the Code. When determining any sanctions to be imposed, the Code Governance Committee will consider:
+Part 13:
+Enforcement, sanctions and compliance
+a. the appropriateness of the sanction; b. if we have not acted on — or have taken too long to act on — a request from the Code Governance Committee to remedy a breach; c. if we have breached an undertaking we gave to the Code Governance Committee; d. if we have not taken adequate steps to prevent a Significant Breach from reoccurring; e. if we have not acted with the utmost good faith.</t>
+  </si>
+  <si>
+    <t>171.  Before the Code Governance Committee imposes a sanction on us, it must give us the opportunity to provide a response. We will respond within 10 Business Days.</t>
+  </si>
+  <si>
+    <t>172. The Code Governance Committee must give us written reasons for its final decision.
+Types of sanctions</t>
+  </si>
+  <si>
+    <t>173. As a sanction for our breach of the Code, the Code Governance Committee may require us to do any one, or more, of the following:
+a. take particular rectification steps within a set timeframe; b. audit our compliance with the Code at our own cost; c. advertise to correct something that the Code Governance Committee decides needs correcting.</t>
+  </si>
+  <si>
+    <t>174. The Code Governance Committee may impose additional sanctions for Significant Breaches of the Code, including requiring us to do any one or more of the following:
+a. compensate an individual for any direct financial loss, or damage, we caused them arising from a Significant Breach; b. publish the fact that we have committed a Significant Breach of the Code; c. pay a community benefit payment for a Significant Breach up to a maximum of $100,000. The size of the community benefit payment must be in proportion to our gross written premium and number of customers.</t>
+  </si>
+  <si>
+    <t>175. When requiring us to pay compensation or a community benefit payment, the Code Governance Committee must take into account any compensation awarded by the Australian Financial Complaints Authority or an enforcement agency.
+The Code Governance Committee must also take into account any impending or ongoing investigation by the Australian Securities and Investments Commission.</t>
+  </si>
+  <si>
+    <t>176. The Code Governance Committee will report Significant Breaches or serious misconduct to the Australian Securities and Investments Commission.</t>
+  </si>
+  <si>
+    <t>177. The Australian Financial Complaints Authority may report possible Code breaches to the Code Governance Committee.</t>
+  </si>
+  <si>
+    <t>178. The Code Governance Committee’s decisions and sanctions are binding on us.
+Our compliance with the Code</t>
+  </si>
+  <si>
+    <t>179. We will have a governance process in place to report to our Board or our executive management, on our compliance with the Code.</t>
+  </si>
+  <si>
+    <t>180. We will have appropriate systems and processes in place to enable the Code Governance Committee to monitor our compliance with the Code. We will prepare an annual compliance report to the Code Governance Committee on our compliance with the Code.</t>
+  </si>
+  <si>
+    <t>181.  If we identify a Significant Breach of the Code, then we will report it to the Code Governance Committee within 10 Business Days.</t>
+  </si>
+  <si>
+    <t>182. We will cooperate with the Code Governance Committee in its review of our compliance with the Code and its investigations of any breaches of the Code.
+Promoting the Code</t>
+  </si>
+  <si>
+    <t>183. The Insurance Council of Australia is responsible for promoting the Code to customers and to industry participants that have not yet adopted the Code.</t>
+  </si>
+  <si>
+    <t>184. The Insurance Council of Australia will work with the Code Governance Committee, the Australian Securities and Investments Commission, relevant regulators and other stakeholders to encourage all general insurers and other industry participants conducting business in Australia to adopt the Code.</t>
+  </si>
+  <si>
+    <t>185. We will work with the Insurance Council of Australia to promote and champion the Code.</t>
+  </si>
+  <si>
+    <t>186. We will:
+a. provide information about the Code and the Code Governance Committee on our websites and in our Retail Insurance Product Information. We will also provide this information in other places where b.
+work with the Insurance Council of Australia to provide general information to help you access insurance products; c. work with the Insurance Council of Australia to initiate programs to and the insurance industry; and d. support the Insurance Council of Australia’s initiatives aimed at education on general insurance.
+Reviewing and improving the Code</t>
+  </si>
+  <si>
+    <t>187. The Insurance Council of Australia will consult with the Code Governance Committee, the Australian Financial Complaints Authority, consumer and industry representatives, relevant regulators and other stakeholders to develop the Code on an ongoing basis.</t>
+  </si>
+  <si>
+    <t>188. At least every 3 years the Insurance Council of Australia will commission a formal, independent review of the Code.</t>
+  </si>
+  <si>
+    <t>189. If the Code Governance Committee believes the Code is not meeting the objectives outlined in part 1 of the Code, then the Code Governance Committee may recommend to the Board of the Insurance Council of Australia that the Code should be reviewed.</t>
+  </si>
+  <si>
+    <t>190. The Code Governance Committee may, in its quarterly reports to the Board of the Insurance Council of Australia, make recommendations about any one or more of the following:
+a. Code improvements, Code related issues and matters of importance as a response to its monitoring and enforcement; b. promoting the Code; c. education and training relevant to the operation of the Code; d. the Insurance Council of Australia’s industry Catastrophe coordination arrangements; and e. the Complaints process.</t>
+  </si>
+  <si>
+    <t>191. We must comply with any additional obligations and binding standards that the Insurance Council of Australia introduces to the Code.</t>
+  </si>
+  <si>
+    <t>192. The Insurance Council of Australia may issue non-binding best practice guides to help us meet our obligations under the Code.
+Part 14:
+Promoting, reviewing and improving the Code we consider it appropriate to do so;
+Paragraph 73 of the Code states: If we appoint an Investigator or Employee to investigate your claim, then within 5 Business Days we will tell you that we have appointed them and what their role is. When we appoint an Investigator or Employee to investigate your claim then the investigation process will comply with these claims investigation standards.
+General investigation obligations</t>
+  </si>
+  <si>
+    <t>193. If we appoint an Investigator, or Employee, to investigate your claim, then we will make sure that they investigate:
+a. only those matters they need to investigate; and b. in an appropriate and respectful manner.</t>
+  </si>
+  <si>
+    <t>194. We have a quality assurance program to regularly monitor and review our investigations. That program might include reviews of:
+a. recordings, statements, affidavits or transcripts of interviews; b. Investigators’ records of investigation activities; and c. Complaints about investigations, including disputes referred to the Australian Financial Complaints Authority.</t>
+  </si>
+  <si>
+    <t>195. Our quality assurance program will include reviews of our non-genuine claims indicators to make sure they remain relevant, appropriate and do not discriminate — we review these at least once a year.</t>
+  </si>
+  <si>
+    <t>196. If an investigation has gone on for 4 months, then we will have your claim independently reviewed by an Employee with appropriate authority, knowledge or experience. We will inform you if this happens.</t>
+  </si>
+  <si>
+    <t>197. During the review, the Employee will determine if there is sufficient cause for the investigation into your claim to continue. If it is determined that the investigation should stop, then your claim will be referred for a decision as set out in part 8.</t>
+  </si>
+  <si>
+    <t>198. The review process will not exceed 30 Calendar Days. If we do not complete the review and notify you of the outcome within that time, we will tell you in writing about our Complaints process.</t>
+  </si>
+  <si>
+    <t>199. After the review, we will tell you in writing, why we have not been able to make a decision on your claim and any information we still need that we do not have.</t>
+  </si>
+  <si>
+    <t>200. To ensure our investigations are appropriately focused:
+a. we will ensure that any requests to you for more information, or documents, are reasonable and relevant to the claim under investigation. We will:
+i.  use our best endeavours to do that in one request; ii.  tell you why we need the information that we are requesting.
+b. when we give our Investigators and Employees authority and instructions in relation to your claim, we will:
+i.  clearly limit the purpose of the investigation to the claim in question; ii.  carefully define their scope about the type of information we are requesting and the period covering the request.</t>
+  </si>
+  <si>
+    <t>201. Before we first start the investigation of your claim, we will discuss with you why your claim is being investigated. We will Part 15:
+Claims investigation standards
+train our Employees about how to have these conversations and the information they need to discuss with you.</t>
+  </si>
+  <si>
+    <t>202. Before we first start the investigation of your claim, we will tell you, verbally and in writing:
+a. about our claims investigations process; b. who is your primary contact for the investigation and their details; c. the role and responsibility of the Investigator or any Employee that has been appointed to investigate your claim; d. when to expect to hear from the Investigator or Employee — and what to do if you do not hear from them within that timeframe; e. that within 10 Business Days after we have received all relevant information and completed all of our enquiries, we will tell you if we are going to pay your claim, unless an exception in the Code applies; f. your rights and responsibilities under the policy during the investigation; g. about our Complaints process.</t>
+  </si>
+  <si>
+    <t>203. If we need your authority to access information from someone else, then we will explain to you why we think you should give us that authority.</t>
+  </si>
+  <si>
+    <t>204. At least every 20 Business Days, we will update you about the investigation’s process.
+Before any formal interview</t>
+  </si>
+  <si>
+    <t>205. If we need to formally interview you as part of the investigation, then before the interview starts, we will tell you in writing:
+a. the purpose of the interview; b. your rights and responsibilities during the interview; c. your right to have an interpreter — free of charge — to translate any information given to you and any answers you provide; d. who will conduct the interview — and their contact details; e. if an Investigator is appointed, that they are acting on our behalf; f. how long the Investigator expects the interview to take; g. our contact details, so you can contact us with any questions about the interview, the Investigator or the Employee appointed to investigate your claim; h. your right to have a legal representative or a support person, who may be a family member, friend or other person, to support you through the interview but may not answer questions on your behalf; and i.  how the interview is to be recorded.</t>
+  </si>
+  <si>
+    <t>206. If you have asked us to communicate through a representative, then we will tell the Investigator, or Employee appointed to investigate your claim, to contact the representative first. If they cannot make contact with the representative within a reasonable time, then they will contact you.</t>
+  </si>
+  <si>
+    <t>207. If an independent interpreter is needed either for you, or for us, we will arrange for this at our cost.</t>
+  </si>
+  <si>
+    <t>208. If you tell us, or we identify, that you need additional support or have other particular needs, then we will arrange for the Investigator or Employee to be someone who we are satisfied has appropriate training or experience to conduct the interview in light of those needs.</t>
+  </si>
+  <si>
+    <t>209. If you request for the Investigator, or Employee appointed to investigate your claim, to be the same gender as you we will tell you if we can arrange for this.
+We may not be able to do this if it is not reasonably practical for us to do so.</t>
+  </si>
+  <si>
+    <t>210. When we are arranging the interview, we will tell you:
+a. several possible convenient locations, including your home, where the interview can occur, and that you can suggest another location, provided it is a reasonable place for both you and the Investigator or Employee; b. that you can schedule the interview for a time and date that suits you.</t>
+  </si>
+  <si>
+    <t>211.  If we intend to interview (or our Investigators or Employees inform us that
+they wish to interview) someone who is under 18, then we will:
+a. assess whether the interview is necessary and whether the interviewee is capable of distinguishing truth from fiction. We will use trained professionals to assess this and they will record how they made that assessment; b. require any Investigator or Employee to clearly set out the scope of the interview; c. require any Investigator or Employee conducting the interview to obtain our written approval to the interview and the scope of the interview before interviewing the person who is under 18; d. require any Investigator or Employee conducting the interview to obtain our written approval before expanding the scope of the interview beyond what we consented to — that approval may be given only by one of our Employees with appropriate experience and training; e. use an Investigator or Employee who we are satisfied has appropriate training or experience to conduct the interview; f. make sure that any interview takes place only in the presence of the interviewee’s parent, guardian or responsible adult; and g. make sure that the Investigator pauses the interview:
+i.  if they are aware that the interviewee is distressed by the interview process; or ii.  at the request of the interviewee, parent, guardian or responsible adult.
+During the formal interview</t>
+  </si>
+  <si>
+    <t>212. When the interview happens, the Investigator, or Employee appointed to investigate your claim, will ask you a series of questions about the information contained in the interview consent form. Those questions are designed to make sure we have your consent to the interview (or not).</t>
+  </si>
+  <si>
+    <t>213. We require our Investigators or Employees appointed to investigate your claim, to conduct all interviews in an objective, honest, efficient, transparent and fair manner at all times.</t>
+  </si>
+  <si>
+    <t>214. A single interview sitting may only last for up to 90 minutes.</t>
+  </si>
+  <si>
+    <t>215. If another interview time is needed, it will not be organised without at least a 24 hour break, unless otherwise agreed.</t>
+  </si>
+  <si>
+    <t>216. If the total interview time required is over 4 hours, the Investigator or the Employee appointed to investigate your claim must obtain written consent from us. In that written consent, we will provide the reasons why this time extension is needed.</t>
+  </si>
+  <si>
+    <t>217.  If during the interview it becomes apparent that an interpreter is needed either for you, or for us, (even though one had not previously been requested or arranged), then the Investigator or Employee will:
+a. pause the interview; and b. restart it at a later time, or date, once an independent interpreter has been arranged.</t>
+  </si>
+  <si>
+    <t>218. If during the interview you need additional support (for example a lawyer, consumer representative or a friend), even though one had not previously been requested or arranged, then the Investigator or Employee will:
+a. pause the interview; b. advise you of the support person’s role in the interview process in accordance with paragraph 205(h); and c. restart the interview at a later time, or date, once the support person has been arranged.</t>
+  </si>
+  <si>
+    <t>219. We will offer you a 5 minute break in the interview every 30 minutes. However, if you tell us — or we identify — that you are experiencing vulnerability, then there will be a 5 minute break every 30 minutes.
+Any break is a time-out and is not included in the 90 minute period referred to under paragraph 214.</t>
+  </si>
+  <si>
+    <t>220. Also, you can request additional breaks and stop the interview early and reschedule if needed.</t>
+  </si>
+  <si>
+    <t>221. The Investigator or Employee must record all offers of breaks, and the interviewee’s responses.
+After the formal interview</t>
+  </si>
+  <si>
+    <t>222. We will offer you a transcript of the formal interview (or a digital copy of the recorded interview), and it will be given to you for free. You can also request this at a later time and it will be provided for free.</t>
+  </si>
+  <si>
+    <t>223. Also, if we need to interview you more than once, then before the second or any later interview, we will give you a copy of the record of your previous interview.
+External Investigators only</t>
+  </si>
+  <si>
+    <t>224. Our contracts with Investigators will set out standards about how they are to conduct themselves, and what they need to do, when investigating people who may be vulnerable.</t>
+  </si>
+  <si>
+    <t>225. If we appoint an Investigator to help us with your claim, then we will:
+a. give them written instructions about each investigation; b. confirm any changes to our instructions; and c. require them to get our consent before they exceed their existing instructions.</t>
+  </si>
+  <si>
+    <t>226. We require our Investigators to:
+a. record the requests they make to individuals for written authorisation to access the individual’s personal information that is held by other parties; and b. to provide those records to us at the end of their investigation.</t>
+  </si>
+  <si>
+    <t>227. Before we authorise an Investigator to investigate or interview a person who may be vulnerable, they will have received training on how to work with vulnerable customers.</t>
+  </si>
+  <si>
+    <t>228. We keep an up-to-date register of our Investigators’ licences, including their expiry dates. We do this to make sure the licences of any Investigators we engage are valid and current.</t>
+  </si>
+  <si>
+    <t>229. Our Investigators must make or retain contemporaneous records in writing of all investigation activities, including but not limited to details of:
+a. conversations held in person; b. telephone conversations; c. unanswered telephone calls — including any messages left; d. all written communications sent — whether: letters, faxes, emails etc.; e. their travel; f. interviews and statements obtained; and g. any electronic checks — including government and social media sites, for example: internet, land titles, Facebook, or business affairs.</t>
+  </si>
+  <si>
+    <t>230. We and/or the organisations that provide our Investigators, must keep these records for at least 7 years.</t>
+  </si>
+  <si>
+    <t>231. We require all our Investigators:
+a. to collect information only if they reasonably believe it is relevant to their investigation; b. to comply with any relevant law; c. to not use illegal means or methods to carry out the investigation; d. to not induce someone to perform a task, or activity, that they would not have performed without the involvement of the Investigator; e. to not make any threat, promise or inducement to any person when conducting an investigation on our behalf; f. to comply with the standards in this document that are relevant to their activities performed on our behalf; and g. to obtain authority by the insurer before alleging fraud.
+Surveillance</t>
+  </si>
+  <si>
+    <t>232. Before we authorise any surveillance of you, we:
+a. make sure that alternative methods of
+verifying the relevant information the surveillance would relate to have been considered; b. must reasonably believe that your claim appears to be inconsistent with the information available to us — and we must record our reasons for this belief; and c. arrange for a suitably experienced Employee to review and approve the request for surveillance.</t>
+  </si>
+  <si>
+    <t>233. We will not conduct surveillance of you:
+a. inside any court, or other judicial facility; b. in any medical, or related facility; c. in any bathroom, change room, or lactation room; d. inside your house; e. at a business premises — unless it is open to the public; f. where prohibited by relevant law.</t>
+  </si>
+  <si>
+    <t>234. We will stop surveillance of you if we become aware that you have a pre- existing mental health condition.</t>
+  </si>
+  <si>
+    <t>235. We will require our Investigators to not communicate with your neighbours, or your work colleagues, in a way that might — directly, or indirectly — reveal that surveillance will be, is being, or has been, conducted.
+Interviewer name and contact details:
+Interviewee’s name and contact details:
+[If under 18 parent, guardian or responsible adult] Insurer’s details:
+Subject matter of interview:
+Need an interpreter, lawyer or support person?
+You can have an interpreter, legal representative or other support person present during your interview.
+If you would like to arrange this, then please:
+•  let the Investigator know as soon as possible; and •  confirm your request below in writing.
+Your privacy statement, acknowledgement and consent If authority to access information from third parties is required, the following may be provided:
+•  scope of authority •  type of information to be requested •  period of information requested •  impact on the claim if the information is not provided •  date of issue and expiry of authority Your interview preferences statement I agree to be interviewed by the Investigator named above — who is a representative of                                                                    in relation to the above matter.
+After discussing my options with the Investigator, I agree to: (Please select) the interview being digitally audio recorded the interview being digitally video recorded other (please write in) I would like to be provided with:
+a typed statement of the interview a handwritten statement of the interview Signature:
+Date Guide: Interview consent form
+Business Days are Monday to Friday, excluding public holidays.
+Calendar Day means any day, including weekends and public holidays.
+Catastrophe means an event declared by the Insurance Council of Australia to be a Catastrophe - for example fire, flood, earthquake, cyclone, severe storm, or hail, resulting in a large number of insurance claims and involving multiple insurers.
+Code means the General Insurance Code of Practice 2020.
+Collection Agent means a person, company or entity who is not our Employee that we contract to recover money owing to us.
+Complaint means an expression of dissatisfaction made to us, related to our products or services, our staff, or the handling of a Complaint where a response or resolution is explicitly or implicitly expected or legally required. A Complaint also includes such expressions of dissatisfaction made about us on a social media channel or account owned or controlled by us, where the person making the Complaint is both identifiable and contactable.
+Consumer Credit Insurance means insurance as defined in regulation 7.1.15 under the Corporations Regulations 2001, but it excludes:
+a. Consumer Credit Insurance sold through motor dealer intermediaries; and b. Consumer Credit Insurance sold alongside a refinanced loan where Consumer Credit Insurance has been purchased with the original loan.</t>
+  </si>
+  <si>
+    <t>Distributor means a person, company or entity when acting on our behalf, that is not an Employee, and; a. is authorised to provide financial services, other than a claims handling and settling service,  under our Australian Financial Services Licence, in accordance with the Corporations Act 2001; or b. has authority to issue, vary or dispose of, a general insurance product covered by this Code under a binder with us (excluding an interim contract).
+Domestic Builders Insurance and Domestic Builders Warranty/Indemnity Insurance means insurance as defined by the relevant State or Territory legislation.
+Employee means a person employed either:
+a. by us; or b. by a related entity that provides services to which this Code applies.
+External Expert means:
+a. a company, entity, or a person who is not our Employee or a Service Supplier; and b. that we contract solely to provide an expert opinion about the likely cause of your loss or damage.
+Extraordinary Catastrophe means a Catastrophe that is so significant in size or magnitude or one that coincides with multiple other Catastrophes that the Board of the Insurance Council of Australia declares it to be extraordinary.
+Financial Hardship means you have difficulty meeting your financial obligations to us.
+in writing means a communication conveyed by any one or more of mail, email, facsimile, text message, or a document sent or given to the relevant person.
+Instalment Policy means a Retail Insurance policy for which the premium is payable by 7 or more instalments in a year, as defined in the Insurance Contracts Act 1984.
+Insured means a person, company or entity holding, or seeking to hold, a general insurance product covered by this Code. It excludes a Third Party Beneficiary.
+Investigator means:
+a. a company, entity, or a person who is not our Employee; and Part 16:
+Definitions
+b. that we contract to verify the circumstances relating to your claim.
+Loss Assessor or Loss Adjuster means:
+a. a company, entity, or a person who is not our Employee; and b. that we contract to:
+i.
+examine the circumstances of your claim; ii. assess the damage or loss; iii. determine whether your claim is covered under your policy; iv. assist in obtaining a repair quote, or a replacement quote; and v.
+help settle the claim.
+Marine Insurance means insurance to which the Marine Insurance Act 1909 applies. The Code applies to pleasure craft covered by the Insurance Contracts Act 1984.
+Medical Indemnity Insurance means medical indemnity cover for health care professionals under a contract of insurance covered by the Medical Indemnity (Prudential Supervision and Product Standards) Act 2003.
+Motor Vehicle Injury Insurance means insurance that covers personal injury or death arising out of the use of a motor vehicle, including cover for the injury or death of a driver of a motor vehicle which is caused by the fault of that person when driving.</t>
+  </si>
+  <si>
+    <t>No Claims Bonus, No Claims Discount or No Claims Entitlement means a discount on discount increases (up to a maximum level) for each consecutive insurance period during which you do not make:
+a. a claim about something involving your fault; or b. a claim that we do not pay.
+Pressure Selling means unethical, misleading, or extended sales techniques that place customers under pressure, or that limit their ability to make an informed purchase decision. This includes the use of techniques to coerce a customer into taking out a policy they do not wish to buy.
+Retail Insurance means a general insurance product that is provided to, or to be provided to, an individual or for use in connection with a Small Business, and is one of the following types:
+a. a motor vehicle insurance product (Regulation 7.1.11); b. a home building insurance product (Regulation 7.1.12); c. a home contents insurance product (Regulation 7.1.13); d. a sickness and accident insurance product (Regulation 7.1.14); e. a Consumer Credit Insurance product (Regulation 7.1.15); f. a travel insurance product (Regulation 7.1.16); g. a personal and domestic property insurance product (Regulation 7.1.17) as Corporations Act 2001 and the relevant Regulations.
+Service Supplier means an Investigator, Loss Assessor or Loss Adjuster, Collection Agent, or a person, company or entity who is not our Employee but is contracted by us to manage your claim on our behalf (including a broker who manages claims for us) and any of their sub-contractors who we have approved and who are also acting on our behalf.
+means a breach that is a. the number and frequency of similar previous breaches; b. the impact of the breach, or likely breach, on our ability to provide our services; c. the extent to which the breach, or likely breach, indicates that our arrangements to ensure compliance with the Code are inadequate; d.
+caused by the breach; and e. the duration of the breach.
+Small Business means a business that employs:
+a. less than 100 people, if the business is or includes the manufacture of goods; or b. otherwise, less than 20 people.
+Retail Insurance Product Information means any one of the product disclosure statement, certiﬁcate of insurance, covering letter,
+covering email or other documents which are
+provided to you in connection with the issue of a Retail Insurance product.
+Third Party Beneficiary means a person, company or entity who is not an Insured but who is seeking to be, is specified to be, or is referred to as, a person to whom the benefit of the insurance cover extends. The relevant product must be covered by this Code. The person, company or entity may be specified by, or referred to by, name or otherwise.
+we, us or our means the organisation that has adopted this Code.
+Wholesale Insurance means a general insurance product covered by the Code which is not Retail Insurance.</t>
+  </si>
+  <si>
+    <t>Workers Compensation Insurance means insurance that covers an employer’s liability to pay compensation for an employment-related personal injury.
+you or your means an Insured or Third Party Beneficiary, or as otherwise stated in relation to particular paragraphs of this Code.
+Insurance Council of Australia The Insurance Council of Australia is the representative body of the general insurance industry in Australia. Its members represent about 95 per cent of total premium income written by private sector general insurers.
+PO Box R1832 Royal Exchange Sydney NSW 1225 ABN 50 005 617 318 General enquiries:
+8.30am to 5pm Monday to Friday 02 9253 5100 or 1300 728 228 www.insurancecouncil.com.au Published 1 October 2023 All images, content and design are the Copyright of the Insurance Council of Australia 2021.</t>
+  </si>
+  <si>
+    <t>obligation</t>
+  </si>
+  <si>
+    <t>prohibition</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>conditional</t>
+  </si>
+  <si>
     <t>timeframe</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Synthetic Compliance Rules #1</t>
+  </si>
+  <si>
     <t>Insurance Compliance Rules</t>
+  </si>
+  <si>
+    <t>TravelTest</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -218,14 +1233,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -513,16 +1520,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.77734375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E263"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,504 +1538,3063 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>270</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>271</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" t="s">
+        <v>272</v>
+      </c>
+      <c r="E30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
       </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="E38" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
         <v>43</v>
       </c>
+      <c r="E40" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>17</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>34</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>72</v>
+      </c>
+      <c r="E69" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>41</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>42</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="E72" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>43</v>
+      </c>
+      <c r="B73" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>46</v>
+      </c>
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+      <c r="E76" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>47</v>
+      </c>
+      <c r="B77" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s">
+        <v>81</v>
+      </c>
+      <c r="E78" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>50</v>
+      </c>
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>51</v>
+      </c>
+      <c r="B81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>53</v>
+      </c>
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>54</v>
+      </c>
+      <c r="B84" t="s">
+        <v>87</v>
+      </c>
+      <c r="E84" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>55</v>
+      </c>
+      <c r="B85" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>56</v>
+      </c>
+      <c r="B86" t="s">
+        <v>89</v>
+      </c>
+      <c r="E86" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>57</v>
+      </c>
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="E87" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>91</v>
+      </c>
+      <c r="E88" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>59</v>
+      </c>
+      <c r="B89" t="s">
+        <v>92</v>
+      </c>
+      <c r="E89" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>60</v>
+      </c>
+      <c r="B90" t="s">
+        <v>93</v>
+      </c>
+      <c r="E90" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>61</v>
+      </c>
+      <c r="B91" t="s">
+        <v>94</v>
+      </c>
+      <c r="E91" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>95</v>
+      </c>
+      <c r="E92" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>63</v>
+      </c>
+      <c r="B93" t="s">
+        <v>96</v>
+      </c>
+      <c r="E93" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>64</v>
+      </c>
+      <c r="B94" t="s">
+        <v>97</v>
+      </c>
+      <c r="E94" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>65</v>
+      </c>
+      <c r="B95" t="s">
+        <v>98</v>
+      </c>
+      <c r="E95" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>66</v>
+      </c>
+      <c r="B96" t="s">
+        <v>99</v>
+      </c>
+      <c r="E96" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s">
+        <v>100</v>
+      </c>
+      <c r="E97" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>68</v>
+      </c>
+      <c r="B98" t="s">
+        <v>101</v>
+      </c>
+      <c r="E98" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>69</v>
+      </c>
+      <c r="B99" t="s">
+        <v>102</v>
+      </c>
+      <c r="E99" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>70</v>
+      </c>
+      <c r="B100" t="s">
+        <v>103</v>
+      </c>
+      <c r="E100" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>104</v>
+      </c>
+      <c r="E101" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>72</v>
+      </c>
+      <c r="B102" t="s">
+        <v>105</v>
+      </c>
+      <c r="E102" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>73</v>
+      </c>
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="E103" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>74</v>
+      </c>
+      <c r="B104" t="s">
+        <v>107</v>
+      </c>
+      <c r="E104" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>75</v>
+      </c>
+      <c r="B105" t="s">
+        <v>108</v>
+      </c>
+      <c r="E105" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>76</v>
+      </c>
+      <c r="B106" t="s">
+        <v>109</v>
+      </c>
+      <c r="E106" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>77</v>
+      </c>
+      <c r="B107" t="s">
+        <v>110</v>
+      </c>
+      <c r="E107" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>78</v>
+      </c>
+      <c r="B108" t="s">
+        <v>111</v>
+      </c>
+      <c r="E108" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>79</v>
+      </c>
+      <c r="B109" t="s">
+        <v>112</v>
+      </c>
+      <c r="E109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>80</v>
+      </c>
+      <c r="B110" t="s">
+        <v>113</v>
+      </c>
+      <c r="E110" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>81</v>
+      </c>
+      <c r="B111" t="s">
+        <v>114</v>
+      </c>
+      <c r="E111" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>82</v>
+      </c>
+      <c r="B112" t="s">
+        <v>115</v>
+      </c>
+      <c r="E112" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>83</v>
+      </c>
+      <c r="B113" t="s">
+        <v>116</v>
+      </c>
+      <c r="E113" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>84</v>
+      </c>
+      <c r="B114" t="s">
+        <v>117</v>
+      </c>
+      <c r="E114" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>85</v>
+      </c>
+      <c r="B115" t="s">
+        <v>118</v>
+      </c>
+      <c r="E115" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>86</v>
+      </c>
+      <c r="B116" t="s">
+        <v>119</v>
+      </c>
+      <c r="E116" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>87</v>
+      </c>
+      <c r="B117" t="s">
+        <v>120</v>
+      </c>
+      <c r="E117" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>88</v>
+      </c>
+      <c r="B118" t="s">
+        <v>121</v>
+      </c>
+      <c r="E118" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>89</v>
+      </c>
+      <c r="B119" t="s">
+        <v>122</v>
+      </c>
+      <c r="E119" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>90</v>
+      </c>
+      <c r="B120" t="s">
+        <v>123</v>
+      </c>
+      <c r="E120" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>91</v>
+      </c>
+      <c r="B121" t="s">
+        <v>124</v>
+      </c>
+      <c r="E121" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>92</v>
+      </c>
+      <c r="B122" t="s">
+        <v>125</v>
+      </c>
+      <c r="E122" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>93</v>
+      </c>
+      <c r="B123" t="s">
+        <v>126</v>
+      </c>
+      <c r="E123" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>94</v>
+      </c>
+      <c r="B124" t="s">
+        <v>127</v>
+      </c>
+      <c r="E124" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>95</v>
+      </c>
+      <c r="B125" t="s">
+        <v>128</v>
+      </c>
+      <c r="E125" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>96</v>
+      </c>
+      <c r="B126" t="s">
+        <v>129</v>
+      </c>
+      <c r="E126" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <v>97</v>
+      </c>
+      <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="E127" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>98</v>
+      </c>
+      <c r="B128" t="s">
+        <v>131</v>
+      </c>
+      <c r="E128" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>99</v>
+      </c>
+      <c r="B129" t="s">
+        <v>132</v>
+      </c>
+      <c r="E129" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
+        <v>133</v>
+      </c>
+      <c r="E130" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>101</v>
+      </c>
+      <c r="B131" t="s">
+        <v>134</v>
+      </c>
+      <c r="E131" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>102</v>
+      </c>
+      <c r="B132" t="s">
+        <v>135</v>
+      </c>
+      <c r="E132" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>103</v>
+      </c>
+      <c r="B133" t="s">
+        <v>136</v>
+      </c>
+      <c r="E133" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>104</v>
+      </c>
+      <c r="B134" t="s">
+        <v>137</v>
+      </c>
+      <c r="E134" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>105</v>
+      </c>
+      <c r="B135" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>106</v>
+      </c>
+      <c r="B136" t="s">
+        <v>139</v>
+      </c>
+      <c r="E136" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>107</v>
+      </c>
+      <c r="B137" t="s">
+        <v>140</v>
+      </c>
+      <c r="E137" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>108</v>
+      </c>
+      <c r="B138" t="s">
+        <v>141</v>
+      </c>
+      <c r="E138" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>109</v>
+      </c>
+      <c r="B139" t="s">
+        <v>142</v>
+      </c>
+      <c r="E139" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>110</v>
+      </c>
+      <c r="B140" t="s">
+        <v>143</v>
+      </c>
+      <c r="E140" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>111</v>
+      </c>
+      <c r="B141" t="s">
+        <v>144</v>
+      </c>
+      <c r="E141" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>112</v>
+      </c>
+      <c r="B142" t="s">
+        <v>145</v>
+      </c>
+      <c r="E142" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>113</v>
+      </c>
+      <c r="B143" t="s">
+        <v>146</v>
+      </c>
+      <c r="E143" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>114</v>
+      </c>
+      <c r="B144" t="s">
+        <v>147</v>
+      </c>
+      <c r="E144" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>115</v>
+      </c>
+      <c r="B145" t="s">
+        <v>148</v>
+      </c>
+      <c r="E145" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>116</v>
+      </c>
+      <c r="B146" t="s">
+        <v>149</v>
+      </c>
+      <c r="E146" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>117</v>
+      </c>
+      <c r="B147" t="s">
+        <v>150</v>
+      </c>
+      <c r="E147" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>118</v>
+      </c>
+      <c r="B148" t="s">
+        <v>151</v>
+      </c>
+      <c r="E148" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>119</v>
+      </c>
+      <c r="B149" t="s">
+        <v>152</v>
+      </c>
+      <c r="E149" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>120</v>
+      </c>
+      <c r="B150" t="s">
+        <v>153</v>
+      </c>
+      <c r="E150" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>121</v>
+      </c>
+      <c r="B151" t="s">
+        <v>154</v>
+      </c>
+      <c r="E151" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>122</v>
+      </c>
+      <c r="B152" t="s">
+        <v>155</v>
+      </c>
+      <c r="E152" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>123</v>
+      </c>
+      <c r="B153" t="s">
+        <v>156</v>
+      </c>
+      <c r="E153" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>124</v>
+      </c>
+      <c r="B154" t="s">
+        <v>157</v>
+      </c>
+      <c r="E154" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>125</v>
+      </c>
+      <c r="B155" t="s">
+        <v>158</v>
+      </c>
+      <c r="E155" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>126</v>
+      </c>
+      <c r="B156" t="s">
+        <v>159</v>
+      </c>
+      <c r="E156" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>127</v>
+      </c>
+      <c r="B157" t="s">
+        <v>160</v>
+      </c>
+      <c r="E157" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>128</v>
+      </c>
+      <c r="B158" t="s">
+        <v>161</v>
+      </c>
+      <c r="E158" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>129</v>
+      </c>
+      <c r="B159" t="s">
+        <v>162</v>
+      </c>
+      <c r="E159" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>130</v>
+      </c>
+      <c r="B160" t="s">
+        <v>163</v>
+      </c>
+      <c r="E160" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>131</v>
+      </c>
+      <c r="B161" t="s">
+        <v>164</v>
+      </c>
+      <c r="E161" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>132</v>
+      </c>
+      <c r="B162" t="s">
+        <v>165</v>
+      </c>
+      <c r="E162" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>133</v>
+      </c>
+      <c r="B163" t="s">
+        <v>166</v>
+      </c>
+      <c r="E163" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>134</v>
+      </c>
+      <c r="B164" t="s">
+        <v>167</v>
+      </c>
+      <c r="E164" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>135</v>
+      </c>
+      <c r="B165" t="s">
+        <v>168</v>
+      </c>
+      <c r="E165" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>136</v>
+      </c>
+      <c r="B166" t="s">
+        <v>169</v>
+      </c>
+      <c r="E166" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>137</v>
+      </c>
+      <c r="B167" t="s">
+        <v>170</v>
+      </c>
+      <c r="E167" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>138</v>
+      </c>
+      <c r="B168" t="s">
+        <v>171</v>
+      </c>
+      <c r="E168" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>139</v>
+      </c>
+      <c r="B169" t="s">
+        <v>172</v>
+      </c>
+      <c r="E169" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>140</v>
+      </c>
+      <c r="B170" t="s">
+        <v>173</v>
+      </c>
+      <c r="E170" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171">
+        <v>141</v>
+      </c>
+      <c r="B171" t="s">
+        <v>174</v>
+      </c>
+      <c r="E171" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172">
+        <v>142</v>
+      </c>
+      <c r="B172" t="s">
+        <v>175</v>
+      </c>
+      <c r="E172" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173">
+        <v>143</v>
+      </c>
+      <c r="B173" t="s">
+        <v>176</v>
+      </c>
+      <c r="E173" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174">
+        <v>144</v>
+      </c>
+      <c r="B174" t="s">
+        <v>177</v>
+      </c>
+      <c r="E174" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175">
+        <v>145</v>
+      </c>
+      <c r="B175" t="s">
+        <v>178</v>
+      </c>
+      <c r="E175" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176">
+        <v>146</v>
+      </c>
+      <c r="B176" t="s">
+        <v>179</v>
+      </c>
+      <c r="E176" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177">
+        <v>147</v>
+      </c>
+      <c r="B177" t="s">
+        <v>180</v>
+      </c>
+      <c r="E177" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178">
+        <v>148</v>
+      </c>
+      <c r="B178" t="s">
+        <v>181</v>
+      </c>
+      <c r="E178" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179">
+        <v>149</v>
+      </c>
+      <c r="B179" t="s">
+        <v>182</v>
+      </c>
+      <c r="E179" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180">
+        <v>150</v>
+      </c>
+      <c r="B180" t="s">
+        <v>183</v>
+      </c>
+      <c r="E180" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181">
+        <v>151</v>
+      </c>
+      <c r="B181" t="s">
+        <v>184</v>
+      </c>
+      <c r="E181" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182">
+        <v>152</v>
+      </c>
+      <c r="B182" t="s">
+        <v>185</v>
+      </c>
+      <c r="E182" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183">
+        <v>153</v>
+      </c>
+      <c r="B183" t="s">
+        <v>186</v>
+      </c>
+      <c r="E183" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184">
+        <v>154</v>
+      </c>
+      <c r="B184" t="s">
+        <v>187</v>
+      </c>
+      <c r="E184" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185">
+        <v>155</v>
+      </c>
+      <c r="B185" t="s">
+        <v>188</v>
+      </c>
+      <c r="E185" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186">
+        <v>156</v>
+      </c>
+      <c r="B186" t="s">
+        <v>189</v>
+      </c>
+      <c r="E186" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187">
+        <v>157</v>
+      </c>
+      <c r="B187" t="s">
+        <v>190</v>
+      </c>
+      <c r="E187" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188">
+        <v>158</v>
+      </c>
+      <c r="B188" t="s">
+        <v>191</v>
+      </c>
+      <c r="E188" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189">
+        <v>159</v>
+      </c>
+      <c r="B189" t="s">
+        <v>192</v>
+      </c>
+      <c r="E189" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190">
+        <v>160</v>
+      </c>
+      <c r="B190" t="s">
+        <v>193</v>
+      </c>
+      <c r="E190" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191">
+        <v>161</v>
+      </c>
+      <c r="B191" t="s">
+        <v>194</v>
+      </c>
+      <c r="E191" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192">
+        <v>162</v>
+      </c>
+      <c r="B192" t="s">
+        <v>195</v>
+      </c>
+      <c r="E192" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193">
+        <v>163</v>
+      </c>
+      <c r="B193" t="s">
+        <v>196</v>
+      </c>
+      <c r="E193" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194">
+        <v>164</v>
+      </c>
+      <c r="B194" t="s">
+        <v>197</v>
+      </c>
+      <c r="E194" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195">
+        <v>165</v>
+      </c>
+      <c r="B195" t="s">
+        <v>198</v>
+      </c>
+      <c r="E195" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196">
+        <v>166</v>
+      </c>
+      <c r="B196" t="s">
+        <v>199</v>
+      </c>
+      <c r="E196" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197">
+        <v>167</v>
+      </c>
+      <c r="B197" t="s">
+        <v>200</v>
+      </c>
+      <c r="E197" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198">
+        <v>168</v>
+      </c>
+      <c r="B198" t="s">
+        <v>201</v>
+      </c>
+      <c r="E198" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199">
+        <v>169</v>
+      </c>
+      <c r="B199" t="s">
+        <v>202</v>
+      </c>
+      <c r="E199" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200">
+        <v>170</v>
+      </c>
+      <c r="B200" t="s">
+        <v>203</v>
+      </c>
+      <c r="E200" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201">
+        <v>171</v>
+      </c>
+      <c r="B201" t="s">
+        <v>204</v>
+      </c>
+      <c r="E201" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202">
+        <v>172</v>
+      </c>
+      <c r="B202" t="s">
+        <v>205</v>
+      </c>
+      <c r="E202" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203">
+        <v>173</v>
+      </c>
+      <c r="B203" t="s">
+        <v>206</v>
+      </c>
+      <c r="E203" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204">
+        <v>174</v>
+      </c>
+      <c r="B204" t="s">
+        <v>207</v>
+      </c>
+      <c r="E204" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205">
+        <v>175</v>
+      </c>
+      <c r="B205" t="s">
+        <v>208</v>
+      </c>
+      <c r="E205" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>176</v>
+      </c>
+      <c r="B206" t="s">
+        <v>209</v>
+      </c>
+      <c r="E206" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>177</v>
+      </c>
+      <c r="B207" t="s">
+        <v>210</v>
+      </c>
+      <c r="E207" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208">
+        <v>178</v>
+      </c>
+      <c r="B208" t="s">
+        <v>211</v>
+      </c>
+      <c r="E208" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209">
+        <v>179</v>
+      </c>
+      <c r="B209" t="s">
+        <v>212</v>
+      </c>
+      <c r="E209" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210">
+        <v>180</v>
+      </c>
+      <c r="B210" t="s">
+        <v>213</v>
+      </c>
+      <c r="E210" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211">
+        <v>181</v>
+      </c>
+      <c r="B211" t="s">
+        <v>214</v>
+      </c>
+      <c r="E211" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212">
+        <v>182</v>
+      </c>
+      <c r="B212" t="s">
+        <v>215</v>
+      </c>
+      <c r="E212" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213">
+        <v>183</v>
+      </c>
+      <c r="B213" t="s">
+        <v>216</v>
+      </c>
+      <c r="E213" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214">
+        <v>184</v>
+      </c>
+      <c r="B214" t="s">
+        <v>217</v>
+      </c>
+      <c r="E214" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215">
+        <v>185</v>
+      </c>
+      <c r="B215" t="s">
+        <v>218</v>
+      </c>
+      <c r="E215" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216">
+        <v>186</v>
+      </c>
+      <c r="B216" t="s">
+        <v>219</v>
+      </c>
+      <c r="E216" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217">
+        <v>187</v>
+      </c>
+      <c r="B217" t="s">
+        <v>220</v>
+      </c>
+      <c r="E217" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218">
+        <v>188</v>
+      </c>
+      <c r="B218" t="s">
+        <v>221</v>
+      </c>
+      <c r="E218" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219">
+        <v>189</v>
+      </c>
+      <c r="B219" t="s">
+        <v>222</v>
+      </c>
+      <c r="E219" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220">
+        <v>190</v>
+      </c>
+      <c r="B220" t="s">
+        <v>223</v>
+      </c>
+      <c r="E220" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221">
+        <v>191</v>
+      </c>
+      <c r="B221" t="s">
+        <v>224</v>
+      </c>
+      <c r="E221" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222">
+        <v>192</v>
+      </c>
+      <c r="B222" t="s">
+        <v>225</v>
+      </c>
+      <c r="E222" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223">
+        <v>193</v>
+      </c>
+      <c r="B223" t="s">
+        <v>226</v>
+      </c>
+      <c r="E223" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224">
+        <v>194</v>
+      </c>
+      <c r="B224" t="s">
+        <v>227</v>
+      </c>
+      <c r="E224" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225">
+        <v>195</v>
+      </c>
+      <c r="B225" t="s">
+        <v>228</v>
+      </c>
+      <c r="E225" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226">
+        <v>196</v>
+      </c>
+      <c r="B226" t="s">
+        <v>229</v>
+      </c>
+      <c r="E226" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227">
+        <v>197</v>
+      </c>
+      <c r="B227" t="s">
+        <v>230</v>
+      </c>
+      <c r="E227" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228">
+        <v>198</v>
+      </c>
+      <c r="B228" t="s">
+        <v>231</v>
+      </c>
+      <c r="E228" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229">
+        <v>199</v>
+      </c>
+      <c r="B229" t="s">
+        <v>232</v>
+      </c>
+      <c r="E229" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230">
+        <v>200</v>
+      </c>
+      <c r="B230" t="s">
+        <v>233</v>
+      </c>
+      <c r="E230" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231">
+        <v>201</v>
+      </c>
+      <c r="B231" t="s">
+        <v>234</v>
+      </c>
+      <c r="E231" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232">
+        <v>202</v>
+      </c>
+      <c r="B232" t="s">
+        <v>235</v>
+      </c>
+      <c r="E232" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233">
+        <v>203</v>
+      </c>
+      <c r="B233" t="s">
+        <v>236</v>
+      </c>
+      <c r="E233" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234">
+        <v>204</v>
+      </c>
+      <c r="B234" t="s">
+        <v>237</v>
+      </c>
+      <c r="E234" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235">
+        <v>205</v>
+      </c>
+      <c r="B235" t="s">
+        <v>238</v>
+      </c>
+      <c r="E235" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236">
+        <v>206</v>
+      </c>
+      <c r="B236" t="s">
+        <v>239</v>
+      </c>
+      <c r="E236" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237">
+        <v>207</v>
+      </c>
+      <c r="B237" t="s">
+        <v>240</v>
+      </c>
+      <c r="E237" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238">
+        <v>208</v>
+      </c>
+      <c r="B238" t="s">
+        <v>241</v>
+      </c>
+      <c r="E238" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239">
+        <v>209</v>
+      </c>
+      <c r="B239" t="s">
+        <v>242</v>
+      </c>
+      <c r="E239" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240">
+        <v>210</v>
+      </c>
+      <c r="B240" t="s">
+        <v>243</v>
+      </c>
+      <c r="E240" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241">
+        <v>211</v>
+      </c>
+      <c r="B241" t="s">
+        <v>244</v>
+      </c>
+      <c r="E241" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242">
+        <v>212</v>
+      </c>
+      <c r="B242" t="s">
+        <v>245</v>
+      </c>
+      <c r="E242" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243">
+        <v>213</v>
+      </c>
+      <c r="B243" t="s">
+        <v>246</v>
+      </c>
+      <c r="E243" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244">
+        <v>214</v>
+      </c>
+      <c r="B244" t="s">
+        <v>247</v>
+      </c>
+      <c r="E244" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245">
+        <v>215</v>
+      </c>
+      <c r="B245" t="s">
+        <v>248</v>
+      </c>
+      <c r="E245" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246">
+        <v>216</v>
+      </c>
+      <c r="B246" t="s">
+        <v>249</v>
+      </c>
+      <c r="E246" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247">
+        <v>217</v>
+      </c>
+      <c r="B247" t="s">
+        <v>250</v>
+      </c>
+      <c r="E247" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248">
+        <v>218</v>
+      </c>
+      <c r="B248" t="s">
+        <v>251</v>
+      </c>
+      <c r="E248" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249">
+        <v>219</v>
+      </c>
+      <c r="B249" t="s">
+        <v>252</v>
+      </c>
+      <c r="E249" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250">
+        <v>220</v>
+      </c>
+      <c r="B250" t="s">
+        <v>253</v>
+      </c>
+      <c r="E250" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251">
+        <v>221</v>
+      </c>
+      <c r="B251" t="s">
+        <v>254</v>
+      </c>
+      <c r="E251" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252">
+        <v>222</v>
+      </c>
+      <c r="B252" t="s">
+        <v>255</v>
+      </c>
+      <c r="E252" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253">
+        <v>223</v>
+      </c>
+      <c r="B253" t="s">
+        <v>256</v>
+      </c>
+      <c r="E253" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254">
+        <v>224</v>
+      </c>
+      <c r="B254" t="s">
+        <v>257</v>
+      </c>
+      <c r="E254" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255">
+        <v>225</v>
+      </c>
+      <c r="B255" t="s">
+        <v>258</v>
+      </c>
+      <c r="E255" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256">
+        <v>226</v>
+      </c>
+      <c r="B256" t="s">
+        <v>259</v>
+      </c>
+      <c r="E256" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257">
+        <v>227</v>
+      </c>
+      <c r="B257" t="s">
+        <v>260</v>
+      </c>
+      <c r="E257" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258">
+        <v>228</v>
+      </c>
+      <c r="B258" t="s">
+        <v>261</v>
+      </c>
+      <c r="E258" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259">
+        <v>229</v>
+      </c>
+      <c r="B259" t="s">
+        <v>262</v>
+      </c>
+      <c r="E259" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260">
+        <v>230</v>
+      </c>
+      <c r="B260" t="s">
+        <v>263</v>
+      </c>
+      <c r="E260" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261">
+        <v>231</v>
+      </c>
+      <c r="B261" t="s">
+        <v>264</v>
+      </c>
+      <c r="E261" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262">
+        <v>232</v>
+      </c>
+      <c r="B262" t="s">
+        <v>265</v>
+      </c>
+      <c r="E262" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263">
+        <v>233</v>
+      </c>
+      <c r="B263" t="s">
+        <v>266</v>
+      </c>
+      <c r="E263" t="s">
+        <v>276</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/POC/regulation_chunks.xlsx
+++ b/backend/POC/regulation_chunks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="292">
   <si>
     <t>chunk_id</t>
   </si>
@@ -1162,6 +1162,42 @@
 8.30am to 5pm Monday to Friday 02 9253 5100 or 1300 728 228 www.insurancecouncil.com.au Published 1 October 2023 All images, content and design are the Copyright of the Insurance Council of Australia 2021.</t>
   </si>
   <si>
+    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
+  </si>
+  <si>
+    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
+  </si>
+  <si>
+    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
+  </si>
+  <si>
+    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
+  </si>
+  <si>
+    <t>11 Verification records shall be retained for a minimum period of seven years from the date of merchant account closure.</t>
+  </si>
+  <si>
+    <t>12 This chapter outlines the obligations of payment service providers with respect to consumer data collected during payment processing.</t>
+  </si>
+  <si>
+    <t>13 Payment service providers shall implement adequate technical and organizational safeguards to protect consumer data against unauthorized access, disclosure, or destruction.</t>
+  </si>
+  <si>
+    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. Without exceptions every payment services are mportant.</t>
+  </si>
+  <si>
+    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. obligation</t>
+  </si>
+  <si>
+    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business. obligation</t>
+  </si>
+  <si>
+    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list. prohibition</t>
+  </si>
+  <si>
+    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk. obligation</t>
+  </si>
+  <si>
     <t>obligation</t>
   </si>
   <si>
@@ -1190,6 +1226,15 @@
   </si>
   <si>
     <t>TravelTest</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>t</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1549,13 +1594,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1566,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1583,13 +1628,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1600,13 +1645,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1617,13 +1662,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1634,13 +1679,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1651,13 +1696,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1668,13 +1713,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1685,13 +1730,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1702,13 +1747,13 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1719,13 +1764,13 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1736,13 +1781,13 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1753,13 +1798,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E14" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1770,13 +1815,13 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E15" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1787,13 +1832,13 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E16" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1804,13 +1849,13 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1821,13 +1866,13 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D18" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1838,13 +1883,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D19" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E19" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1855,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D20" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1872,13 +1917,13 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D21" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1889,13 +1934,13 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E22" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1906,13 +1951,13 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E23" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1923,13 +1968,13 @@
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D24" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E24" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1940,13 +1985,13 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D25" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E25" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1957,10 +2002,10 @@
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E26" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1971,13 +2016,13 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E27" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1988,13 +2033,13 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E28" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2005,13 +2050,13 @@
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D29" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E29" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2022,13 +2067,13 @@
         <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D30" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E30" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2039,7 +2084,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2050,7 +2095,7 @@
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2061,7 +2106,7 @@
         <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2072,7 +2117,7 @@
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2083,7 +2128,7 @@
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2094,7 +2139,7 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2105,7 +2150,7 @@
         <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2116,7 +2161,7 @@
         <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2127,7 +2172,7 @@
         <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2138,7 +2183,7 @@
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2149,7 +2194,7 @@
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2160,7 +2205,7 @@
         <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2171,7 +2216,7 @@
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2182,7 +2227,7 @@
         <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2193,7 +2238,7 @@
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2204,7 +2249,7 @@
         <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2215,7 +2260,7 @@
         <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2226,7 +2271,7 @@
         <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2237,7 +2282,7 @@
         <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2248,7 +2293,7 @@
         <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2259,7 +2304,7 @@
         <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2270,7 +2315,7 @@
         <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2281,7 +2326,7 @@
         <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2292,7 +2337,7 @@
         <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2303,7 +2348,7 @@
         <v>58</v>
       </c>
       <c r="E55" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2314,7 +2359,7 @@
         <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2325,7 +2370,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2336,7 +2381,7 @@
         <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2347,7 +2392,7 @@
         <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2358,7 +2403,7 @@
         <v>63</v>
       </c>
       <c r="E60" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2369,7 +2414,7 @@
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2380,7 +2425,7 @@
         <v>65</v>
       </c>
       <c r="E62" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2391,7 +2436,7 @@
         <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2402,7 +2447,7 @@
         <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2413,7 +2458,7 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2424,7 +2469,7 @@
         <v>69</v>
       </c>
       <c r="E66" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2435,7 +2480,7 @@
         <v>70</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2446,7 +2491,7 @@
         <v>71</v>
       </c>
       <c r="E68" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2457,7 +2502,7 @@
         <v>72</v>
       </c>
       <c r="E69" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2468,7 +2513,7 @@
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2479,7 +2524,7 @@
         <v>74</v>
       </c>
       <c r="E71" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2490,7 +2535,7 @@
         <v>75</v>
       </c>
       <c r="E72" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2501,7 +2546,7 @@
         <v>76</v>
       </c>
       <c r="E73" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2512,7 +2557,7 @@
         <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2523,7 +2568,7 @@
         <v>78</v>
       </c>
       <c r="E75" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2534,7 +2579,7 @@
         <v>79</v>
       </c>
       <c r="E76" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2545,7 +2590,7 @@
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2556,7 +2601,7 @@
         <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2567,7 +2612,7 @@
         <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2578,7 +2623,7 @@
         <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2589,7 +2634,7 @@
         <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2600,7 +2645,7 @@
         <v>85</v>
       </c>
       <c r="E82" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2611,7 +2656,7 @@
         <v>86</v>
       </c>
       <c r="E83" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2622,7 +2667,7 @@
         <v>87</v>
       </c>
       <c r="E84" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2633,7 +2678,7 @@
         <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2644,7 +2689,7 @@
         <v>89</v>
       </c>
       <c r="E86" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2655,7 +2700,7 @@
         <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2666,7 +2711,7 @@
         <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2677,7 +2722,7 @@
         <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2688,7 +2733,7 @@
         <v>93</v>
       </c>
       <c r="E90" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2699,7 +2744,7 @@
         <v>94</v>
       </c>
       <c r="E91" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2710,7 +2755,7 @@
         <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2721,7 +2766,7 @@
         <v>96</v>
       </c>
       <c r="E93" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2732,7 +2777,7 @@
         <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2743,7 +2788,7 @@
         <v>98</v>
       </c>
       <c r="E95" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2754,7 +2799,7 @@
         <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2765,7 +2810,7 @@
         <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2776,7 +2821,7 @@
         <v>101</v>
       </c>
       <c r="E98" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2787,7 +2832,7 @@
         <v>102</v>
       </c>
       <c r="E99" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2798,7 +2843,7 @@
         <v>103</v>
       </c>
       <c r="E100" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2809,7 +2854,7 @@
         <v>104</v>
       </c>
       <c r="E101" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2820,7 +2865,7 @@
         <v>105</v>
       </c>
       <c r="E102" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2831,7 +2876,7 @@
         <v>106</v>
       </c>
       <c r="E103" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2842,7 +2887,7 @@
         <v>107</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2853,7 +2898,7 @@
         <v>108</v>
       </c>
       <c r="E105" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2864,7 +2909,7 @@
         <v>109</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2875,7 +2920,7 @@
         <v>110</v>
       </c>
       <c r="E107" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2886,7 +2931,7 @@
         <v>111</v>
       </c>
       <c r="E108" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2897,7 +2942,7 @@
         <v>112</v>
       </c>
       <c r="E109" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2908,7 +2953,7 @@
         <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2919,7 +2964,7 @@
         <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2930,7 +2975,7 @@
         <v>115</v>
       </c>
       <c r="E112" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2941,7 +2986,7 @@
         <v>116</v>
       </c>
       <c r="E113" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2952,7 +2997,7 @@
         <v>117</v>
       </c>
       <c r="E114" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2963,7 +3008,7 @@
         <v>118</v>
       </c>
       <c r="E115" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2974,7 +3019,7 @@
         <v>119</v>
       </c>
       <c r="E116" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2985,7 +3030,7 @@
         <v>120</v>
       </c>
       <c r="E117" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2996,7 +3041,7 @@
         <v>121</v>
       </c>
       <c r="E118" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3007,7 +3052,7 @@
         <v>122</v>
       </c>
       <c r="E119" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3018,7 +3063,7 @@
         <v>123</v>
       </c>
       <c r="E120" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3029,7 +3074,7 @@
         <v>124</v>
       </c>
       <c r="E121" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3040,7 +3085,7 @@
         <v>125</v>
       </c>
       <c r="E122" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3051,7 +3096,7 @@
         <v>126</v>
       </c>
       <c r="E123" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3062,7 +3107,7 @@
         <v>127</v>
       </c>
       <c r="E124" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3073,7 +3118,7 @@
         <v>128</v>
       </c>
       <c r="E125" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3084,7 +3129,7 @@
         <v>129</v>
       </c>
       <c r="E126" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3095,7 +3140,7 @@
         <v>130</v>
       </c>
       <c r="E127" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3106,7 +3151,7 @@
         <v>131</v>
       </c>
       <c r="E128" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3117,7 +3162,7 @@
         <v>132</v>
       </c>
       <c r="E129" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3128,7 +3173,7 @@
         <v>133</v>
       </c>
       <c r="E130" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3139,7 +3184,7 @@
         <v>134</v>
       </c>
       <c r="E131" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3150,7 +3195,7 @@
         <v>135</v>
       </c>
       <c r="E132" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3161,7 +3206,7 @@
         <v>136</v>
       </c>
       <c r="E133" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3172,7 +3217,7 @@
         <v>137</v>
       </c>
       <c r="E134" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3183,7 +3228,7 @@
         <v>138</v>
       </c>
       <c r="E135" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3194,7 +3239,7 @@
         <v>139</v>
       </c>
       <c r="E136" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3205,7 +3250,7 @@
         <v>140</v>
       </c>
       <c r="E137" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3216,7 +3261,7 @@
         <v>141</v>
       </c>
       <c r="E138" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3227,7 +3272,7 @@
         <v>142</v>
       </c>
       <c r="E139" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3238,7 +3283,7 @@
         <v>143</v>
       </c>
       <c r="E140" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3249,7 +3294,7 @@
         <v>144</v>
       </c>
       <c r="E141" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3260,7 +3305,7 @@
         <v>145</v>
       </c>
       <c r="E142" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3271,7 +3316,7 @@
         <v>146</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3282,7 +3327,7 @@
         <v>147</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3293,7 +3338,7 @@
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3304,7 +3349,7 @@
         <v>149</v>
       </c>
       <c r="E146" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3315,7 +3360,7 @@
         <v>150</v>
       </c>
       <c r="E147" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3326,7 +3371,7 @@
         <v>151</v>
       </c>
       <c r="E148" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3337,7 +3382,7 @@
         <v>152</v>
       </c>
       <c r="E149" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3348,7 +3393,7 @@
         <v>153</v>
       </c>
       <c r="E150" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3359,7 +3404,7 @@
         <v>154</v>
       </c>
       <c r="E151" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3370,7 +3415,7 @@
         <v>155</v>
       </c>
       <c r="E152" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3381,7 +3426,7 @@
         <v>156</v>
       </c>
       <c r="E153" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3392,7 +3437,7 @@
         <v>157</v>
       </c>
       <c r="E154" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3403,7 +3448,7 @@
         <v>158</v>
       </c>
       <c r="E155" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3414,7 +3459,7 @@
         <v>159</v>
       </c>
       <c r="E156" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3425,7 +3470,7 @@
         <v>160</v>
       </c>
       <c r="E157" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3436,7 +3481,7 @@
         <v>161</v>
       </c>
       <c r="E158" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3447,7 +3492,7 @@
         <v>162</v>
       </c>
       <c r="E159" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3458,7 +3503,7 @@
         <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3469,7 +3514,7 @@
         <v>164</v>
       </c>
       <c r="E161" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3480,7 +3525,7 @@
         <v>165</v>
       </c>
       <c r="E162" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3491,7 +3536,7 @@
         <v>166</v>
       </c>
       <c r="E163" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3502,7 +3547,7 @@
         <v>167</v>
       </c>
       <c r="E164" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3513,7 +3558,7 @@
         <v>168</v>
       </c>
       <c r="E165" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3524,7 +3569,7 @@
         <v>169</v>
       </c>
       <c r="E166" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3535,7 +3580,7 @@
         <v>170</v>
       </c>
       <c r="E167" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3546,7 +3591,7 @@
         <v>171</v>
       </c>
       <c r="E168" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3557,7 +3602,7 @@
         <v>172</v>
       </c>
       <c r="E169" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3568,7 +3613,7 @@
         <v>173</v>
       </c>
       <c r="E170" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3579,7 +3624,7 @@
         <v>174</v>
       </c>
       <c r="E171" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3590,7 +3635,7 @@
         <v>175</v>
       </c>
       <c r="E172" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3601,7 +3646,7 @@
         <v>176</v>
       </c>
       <c r="E173" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3612,7 +3657,7 @@
         <v>177</v>
       </c>
       <c r="E174" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3623,7 +3668,7 @@
         <v>178</v>
       </c>
       <c r="E175" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3634,7 +3679,7 @@
         <v>179</v>
       </c>
       <c r="E176" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3645,7 +3690,7 @@
         <v>180</v>
       </c>
       <c r="E177" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3656,7 +3701,7 @@
         <v>181</v>
       </c>
       <c r="E178" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3667,7 +3712,7 @@
         <v>182</v>
       </c>
       <c r="E179" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3678,7 +3723,7 @@
         <v>183</v>
       </c>
       <c r="E180" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3689,7 +3734,7 @@
         <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3700,7 +3745,7 @@
         <v>185</v>
       </c>
       <c r="E182" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3711,7 +3756,7 @@
         <v>186</v>
       </c>
       <c r="E183" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3722,7 +3767,7 @@
         <v>187</v>
       </c>
       <c r="E184" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3733,7 +3778,7 @@
         <v>188</v>
       </c>
       <c r="E185" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3744,7 +3789,7 @@
         <v>189</v>
       </c>
       <c r="E186" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3755,7 +3800,7 @@
         <v>190</v>
       </c>
       <c r="E187" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3766,7 +3811,7 @@
         <v>191</v>
       </c>
       <c r="E188" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3777,7 +3822,7 @@
         <v>192</v>
       </c>
       <c r="E189" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3788,7 +3833,7 @@
         <v>193</v>
       </c>
       <c r="E190" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3799,7 +3844,7 @@
         <v>194</v>
       </c>
       <c r="E191" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3810,7 +3855,7 @@
         <v>195</v>
       </c>
       <c r="E192" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3821,7 +3866,7 @@
         <v>196</v>
       </c>
       <c r="E193" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3832,7 +3877,7 @@
         <v>197</v>
       </c>
       <c r="E194" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3843,7 +3888,7 @@
         <v>198</v>
       </c>
       <c r="E195" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3854,7 +3899,7 @@
         <v>199</v>
       </c>
       <c r="E196" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3865,7 +3910,7 @@
         <v>200</v>
       </c>
       <c r="E197" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3876,7 +3921,7 @@
         <v>201</v>
       </c>
       <c r="E198" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3887,7 +3932,7 @@
         <v>202</v>
       </c>
       <c r="E199" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3898,7 +3943,7 @@
         <v>203</v>
       </c>
       <c r="E200" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3909,7 +3954,7 @@
         <v>204</v>
       </c>
       <c r="E201" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3920,7 +3965,7 @@
         <v>205</v>
       </c>
       <c r="E202" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3931,7 +3976,7 @@
         <v>206</v>
       </c>
       <c r="E203" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3942,7 +3987,7 @@
         <v>207</v>
       </c>
       <c r="E204" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3953,7 +3998,7 @@
         <v>208</v>
       </c>
       <c r="E205" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3964,7 +4009,7 @@
         <v>209</v>
       </c>
       <c r="E206" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3975,7 +4020,7 @@
         <v>210</v>
       </c>
       <c r="E207" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3986,7 +4031,7 @@
         <v>211</v>
       </c>
       <c r="E208" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3997,7 +4042,7 @@
         <v>212</v>
       </c>
       <c r="E209" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4008,7 +4053,7 @@
         <v>213</v>
       </c>
       <c r="E210" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4019,7 +4064,7 @@
         <v>214</v>
       </c>
       <c r="E211" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4030,7 +4075,7 @@
         <v>215</v>
       </c>
       <c r="E212" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4041,7 +4086,7 @@
         <v>216</v>
       </c>
       <c r="E213" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4052,7 +4097,7 @@
         <v>217</v>
       </c>
       <c r="E214" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4063,7 +4108,7 @@
         <v>218</v>
       </c>
       <c r="E215" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4074,7 +4119,7 @@
         <v>219</v>
       </c>
       <c r="E216" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4085,7 +4130,7 @@
         <v>220</v>
       </c>
       <c r="E217" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4096,7 +4141,7 @@
         <v>221</v>
       </c>
       <c r="E218" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4107,7 +4152,7 @@
         <v>222</v>
       </c>
       <c r="E219" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4118,7 +4163,7 @@
         <v>223</v>
       </c>
       <c r="E220" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4129,7 +4174,7 @@
         <v>224</v>
       </c>
       <c r="E221" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4140,7 +4185,7 @@
         <v>225</v>
       </c>
       <c r="E222" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4151,7 +4196,7 @@
         <v>226</v>
       </c>
       <c r="E223" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,7 +4207,7 @@
         <v>227</v>
       </c>
       <c r="E224" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4173,7 +4218,7 @@
         <v>228</v>
       </c>
       <c r="E225" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4184,7 +4229,7 @@
         <v>229</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4195,7 +4240,7 @@
         <v>230</v>
       </c>
       <c r="E227" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4206,7 +4251,7 @@
         <v>231</v>
       </c>
       <c r="E228" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4217,7 +4262,7 @@
         <v>232</v>
       </c>
       <c r="E229" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4228,7 +4273,7 @@
         <v>233</v>
       </c>
       <c r="E230" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4239,7 +4284,7 @@
         <v>234</v>
       </c>
       <c r="E231" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4250,7 +4295,7 @@
         <v>235</v>
       </c>
       <c r="E232" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4261,7 +4306,7 @@
         <v>236</v>
       </c>
       <c r="E233" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4272,7 +4317,7 @@
         <v>237</v>
       </c>
       <c r="E234" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4283,7 +4328,7 @@
         <v>238</v>
       </c>
       <c r="E235" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4294,7 +4339,7 @@
         <v>239</v>
       </c>
       <c r="E236" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4305,7 +4350,7 @@
         <v>240</v>
       </c>
       <c r="E237" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4316,7 +4361,7 @@
         <v>241</v>
       </c>
       <c r="E238" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4327,7 +4372,7 @@
         <v>242</v>
       </c>
       <c r="E239" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4338,7 +4383,7 @@
         <v>243</v>
       </c>
       <c r="E240" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4349,7 +4394,7 @@
         <v>244</v>
       </c>
       <c r="E241" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4360,7 +4405,7 @@
         <v>245</v>
       </c>
       <c r="E242" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4371,7 +4416,7 @@
         <v>246</v>
       </c>
       <c r="E243" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4382,7 +4427,7 @@
         <v>247</v>
       </c>
       <c r="E244" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4393,7 +4438,7 @@
         <v>248</v>
       </c>
       <c r="E245" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4404,7 +4449,7 @@
         <v>249</v>
       </c>
       <c r="E246" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4415,7 +4460,7 @@
         <v>250</v>
       </c>
       <c r="E247" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4426,7 +4471,7 @@
         <v>251</v>
       </c>
       <c r="E248" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4437,7 +4482,7 @@
         <v>252</v>
       </c>
       <c r="E249" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4448,7 +4493,7 @@
         <v>253</v>
       </c>
       <c r="E250" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4459,7 +4504,7 @@
         <v>254</v>
       </c>
       <c r="E251" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4470,7 +4515,7 @@
         <v>255</v>
       </c>
       <c r="E252" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4481,7 +4526,7 @@
         <v>256</v>
       </c>
       <c r="E253" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4492,7 +4537,7 @@
         <v>257</v>
       </c>
       <c r="E254" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4503,7 +4548,7 @@
         <v>258</v>
       </c>
       <c r="E255" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4514,7 +4559,7 @@
         <v>259</v>
       </c>
       <c r="E256" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4525,7 +4570,7 @@
         <v>260</v>
       </c>
       <c r="E257" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4536,7 +4581,7 @@
         <v>261</v>
       </c>
       <c r="E258" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4547,7 +4592,7 @@
         <v>262</v>
       </c>
       <c r="E259" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4558,7 +4603,7 @@
         <v>263</v>
       </c>
       <c r="E260" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4569,7 +4614,7 @@
         <v>264</v>
       </c>
       <c r="E261" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4580,7 +4625,7 @@
         <v>265</v>
       </c>
       <c r="E262" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4591,7 +4636,205 @@
         <v>266</v>
       </c>
       <c r="E263" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264">
+        <v>1</v>
+      </c>
+      <c r="B264" t="s">
+        <v>267</v>
+      </c>
+      <c r="E264" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265">
+        <v>2</v>
+      </c>
+      <c r="B265" t="s">
+        <v>268</v>
+      </c>
+      <c r="E265" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266">
+        <v>3</v>
+      </c>
+      <c r="B266" t="s">
+        <v>269</v>
+      </c>
+      <c r="E266" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267">
+        <v>4</v>
+      </c>
+      <c r="B267" t="s">
+        <v>270</v>
+      </c>
+      <c r="E267" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268">
+        <v>5</v>
+      </c>
+      <c r="B268" t="s">
+        <v>271</v>
+      </c>
+      <c r="E268" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269">
+        <v>6</v>
+      </c>
+      <c r="B269" t="s">
+        <v>272</v>
+      </c>
+      <c r="E269" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270">
+        <v>7</v>
+      </c>
+      <c r="B270" t="s">
+        <v>273</v>
+      </c>
+      <c r="E270" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271">
+        <v>1</v>
+      </c>
+      <c r="B271" t="s">
+        <v>274</v>
+      </c>
+      <c r="E271" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272">
+        <v>2</v>
+      </c>
+      <c r="B272" t="s">
+        <v>268</v>
+      </c>
+      <c r="E272" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273">
+        <v>3</v>
+      </c>
+      <c r="B273" t="s">
+        <v>269</v>
+      </c>
+      <c r="E273" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274">
+        <v>4</v>
+      </c>
+      <c r="B274" t="s">
+        <v>270</v>
+      </c>
+      <c r="E274" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275">
+        <v>5</v>
+      </c>
+      <c r="B275" t="s">
+        <v>271</v>
+      </c>
+      <c r="E275" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276">
+        <v>6</v>
+      </c>
+      <c r="B276" t="s">
+        <v>272</v>
+      </c>
+      <c r="E276" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277">
+        <v>7</v>
+      </c>
+      <c r="B277" t="s">
+        <v>273</v>
+      </c>
+      <c r="E277" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278">
+        <v>1</v>
+      </c>
+      <c r="B278" t="s">
+        <v>275</v>
+      </c>
+      <c r="E278" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279">
+        <v>2</v>
+      </c>
+      <c r="B279" t="s">
         <v>276</v>
+      </c>
+      <c r="E279" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280">
+        <v>3</v>
+      </c>
+      <c r="B280" t="s">
+        <v>277</v>
+      </c>
+      <c r="E280" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281">
+        <v>4</v>
+      </c>
+      <c r="B281" t="s">
+        <v>278</v>
+      </c>
+      <c r="E281" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/backend/POC/regulation_chunks.xlsx
+++ b/backend/POC/regulation_chunks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="277">
   <si>
     <t>chunk_id</t>
   </si>
@@ -1162,42 +1162,6 @@
 8.30am to 5pm Monday to Friday 02 9253 5100 or 1300 728 228 www.insurancecouncil.com.au Published 1 October 2023 All images, content and design are the Copyright of the Insurance Council of Australia 2021.</t>
   </si>
   <si>
-    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
-  </si>
-  <si>
-    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
-  </si>
-  <si>
-    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
-  </si>
-  <si>
-    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
-  </si>
-  <si>
-    <t>11 Verification records shall be retained for a minimum period of seven years from the date of merchant account closure.</t>
-  </si>
-  <si>
-    <t>12 This chapter outlines the obligations of payment service providers with respect to consumer data collected during payment processing.</t>
-  </si>
-  <si>
-    <t>13 Payment service providers shall implement adequate technical and organizational safeguards to protect consumer data against unauthorized access, disclosure, or destruction.</t>
-  </si>
-  <si>
-    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. Without exceptions every payment services are mportant.</t>
-  </si>
-  <si>
-    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. obligation</t>
-  </si>
-  <si>
-    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business. obligation</t>
-  </si>
-  <si>
-    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list. prohibition</t>
-  </si>
-  <si>
-    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk. obligation</t>
-  </si>
-  <si>
     <t>obligation</t>
   </si>
   <si>
@@ -1226,15 +1190,6 @@
   </si>
   <si>
     <t>TravelTest</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>t</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1594,13 +1549,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1611,13 +1566,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1628,13 +1583,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1645,13 +1600,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1662,13 +1617,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1679,13 +1634,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D7" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1696,13 +1651,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1713,13 +1668,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1730,13 +1685,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1747,13 +1702,13 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1764,13 +1719,13 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1781,13 +1736,13 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1798,13 +1753,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E14" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1815,13 +1770,13 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1832,13 +1787,13 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1849,13 +1804,13 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1866,13 +1821,13 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D18" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1883,13 +1838,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1900,13 +1855,13 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1917,13 +1872,13 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1934,13 +1889,13 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1951,13 +1906,13 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E23" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1968,13 +1923,13 @@
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E24" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1985,13 +1940,13 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E25" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2002,10 +1957,10 @@
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E26" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2016,13 +1971,13 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D27" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2033,13 +1988,13 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2050,13 +2005,13 @@
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E29" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2067,13 +2022,13 @@
         <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2084,7 +2039,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2095,7 +2050,7 @@
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2106,7 +2061,7 @@
         <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2117,7 +2072,7 @@
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2128,7 +2083,7 @@
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2139,7 +2094,7 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,7 +2105,7 @@
         <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2161,7 +2116,7 @@
         <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2172,7 +2127,7 @@
         <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2183,7 +2138,7 @@
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2194,7 +2149,7 @@
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2205,7 +2160,7 @@
         <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2216,7 +2171,7 @@
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2227,7 +2182,7 @@
         <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2238,7 +2193,7 @@
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2249,7 +2204,7 @@
         <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2260,7 +2215,7 @@
         <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2271,7 +2226,7 @@
         <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2282,7 +2237,7 @@
         <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2293,7 +2248,7 @@
         <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2304,7 +2259,7 @@
         <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2315,7 +2270,7 @@
         <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2326,7 +2281,7 @@
         <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2337,7 +2292,7 @@
         <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2348,7 +2303,7 @@
         <v>58</v>
       </c>
       <c r="E55" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2359,7 +2314,7 @@
         <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2370,7 +2325,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2381,7 +2336,7 @@
         <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2392,7 +2347,7 @@
         <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2403,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="E60" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2414,7 +2369,7 @@
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2425,7 +2380,7 @@
         <v>65</v>
       </c>
       <c r="E62" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2436,7 +2391,7 @@
         <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2447,7 +2402,7 @@
         <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2458,7 +2413,7 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2469,7 +2424,7 @@
         <v>69</v>
       </c>
       <c r="E66" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2480,7 +2435,7 @@
         <v>70</v>
       </c>
       <c r="E67" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2491,7 +2446,7 @@
         <v>71</v>
       </c>
       <c r="E68" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2502,7 +2457,7 @@
         <v>72</v>
       </c>
       <c r="E69" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2513,7 +2468,7 @@
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2524,7 +2479,7 @@
         <v>74</v>
       </c>
       <c r="E71" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2535,7 +2490,7 @@
         <v>75</v>
       </c>
       <c r="E72" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2546,7 +2501,7 @@
         <v>76</v>
       </c>
       <c r="E73" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2557,7 +2512,7 @@
         <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2568,7 +2523,7 @@
         <v>78</v>
       </c>
       <c r="E75" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2579,7 +2534,7 @@
         <v>79</v>
       </c>
       <c r="E76" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2590,7 +2545,7 @@
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2601,7 +2556,7 @@
         <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2612,7 +2567,7 @@
         <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2623,7 +2578,7 @@
         <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2634,7 +2589,7 @@
         <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2645,7 +2600,7 @@
         <v>85</v>
       </c>
       <c r="E82" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2656,7 +2611,7 @@
         <v>86</v>
       </c>
       <c r="E83" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2667,7 +2622,7 @@
         <v>87</v>
       </c>
       <c r="E84" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2678,7 +2633,7 @@
         <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2689,7 +2644,7 @@
         <v>89</v>
       </c>
       <c r="E86" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2700,7 +2655,7 @@
         <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2711,7 +2666,7 @@
         <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2722,7 +2677,7 @@
         <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2733,7 +2688,7 @@
         <v>93</v>
       </c>
       <c r="E90" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2744,7 +2699,7 @@
         <v>94</v>
       </c>
       <c r="E91" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2755,7 +2710,7 @@
         <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2766,7 +2721,7 @@
         <v>96</v>
       </c>
       <c r="E93" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2777,7 +2732,7 @@
         <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2788,7 +2743,7 @@
         <v>98</v>
       </c>
       <c r="E95" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2799,7 +2754,7 @@
         <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2810,7 +2765,7 @@
         <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2821,7 +2776,7 @@
         <v>101</v>
       </c>
       <c r="E98" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2832,7 +2787,7 @@
         <v>102</v>
       </c>
       <c r="E99" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2843,7 +2798,7 @@
         <v>103</v>
       </c>
       <c r="E100" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2854,7 +2809,7 @@
         <v>104</v>
       </c>
       <c r="E101" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2865,7 +2820,7 @@
         <v>105</v>
       </c>
       <c r="E102" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2876,7 +2831,7 @@
         <v>106</v>
       </c>
       <c r="E103" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2887,7 +2842,7 @@
         <v>107</v>
       </c>
       <c r="E104" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2898,7 +2853,7 @@
         <v>108</v>
       </c>
       <c r="E105" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2909,7 +2864,7 @@
         <v>109</v>
       </c>
       <c r="E106" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2920,7 +2875,7 @@
         <v>110</v>
       </c>
       <c r="E107" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2931,7 +2886,7 @@
         <v>111</v>
       </c>
       <c r="E108" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2942,7 +2897,7 @@
         <v>112</v>
       </c>
       <c r="E109" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2953,7 +2908,7 @@
         <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2964,7 +2919,7 @@
         <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2975,7 +2930,7 @@
         <v>115</v>
       </c>
       <c r="E112" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2986,7 +2941,7 @@
         <v>116</v>
       </c>
       <c r="E113" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2997,7 +2952,7 @@
         <v>117</v>
       </c>
       <c r="E114" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3008,7 +2963,7 @@
         <v>118</v>
       </c>
       <c r="E115" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3019,7 +2974,7 @@
         <v>119</v>
       </c>
       <c r="E116" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3030,7 +2985,7 @@
         <v>120</v>
       </c>
       <c r="E117" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3041,7 +2996,7 @@
         <v>121</v>
       </c>
       <c r="E118" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3052,7 +3007,7 @@
         <v>122</v>
       </c>
       <c r="E119" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3063,7 +3018,7 @@
         <v>123</v>
       </c>
       <c r="E120" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3074,7 +3029,7 @@
         <v>124</v>
       </c>
       <c r="E121" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3085,7 +3040,7 @@
         <v>125</v>
       </c>
       <c r="E122" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3096,7 +3051,7 @@
         <v>126</v>
       </c>
       <c r="E123" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3107,7 +3062,7 @@
         <v>127</v>
       </c>
       <c r="E124" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3118,7 +3073,7 @@
         <v>128</v>
       </c>
       <c r="E125" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3129,7 +3084,7 @@
         <v>129</v>
       </c>
       <c r="E126" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3140,7 +3095,7 @@
         <v>130</v>
       </c>
       <c r="E127" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3151,7 +3106,7 @@
         <v>131</v>
       </c>
       <c r="E128" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3162,7 +3117,7 @@
         <v>132</v>
       </c>
       <c r="E129" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3173,7 +3128,7 @@
         <v>133</v>
       </c>
       <c r="E130" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3184,7 +3139,7 @@
         <v>134</v>
       </c>
       <c r="E131" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3195,7 +3150,7 @@
         <v>135</v>
       </c>
       <c r="E132" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3206,7 +3161,7 @@
         <v>136</v>
       </c>
       <c r="E133" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3217,7 +3172,7 @@
         <v>137</v>
       </c>
       <c r="E134" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3228,7 +3183,7 @@
         <v>138</v>
       </c>
       <c r="E135" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3239,7 +3194,7 @@
         <v>139</v>
       </c>
       <c r="E136" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3250,7 +3205,7 @@
         <v>140</v>
       </c>
       <c r="E137" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3261,7 +3216,7 @@
         <v>141</v>
       </c>
       <c r="E138" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3272,7 +3227,7 @@
         <v>142</v>
       </c>
       <c r="E139" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3283,7 +3238,7 @@
         <v>143</v>
       </c>
       <c r="E140" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3294,7 +3249,7 @@
         <v>144</v>
       </c>
       <c r="E141" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3305,7 +3260,7 @@
         <v>145</v>
       </c>
       <c r="E142" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3316,7 +3271,7 @@
         <v>146</v>
       </c>
       <c r="E143" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3327,7 +3282,7 @@
         <v>147</v>
       </c>
       <c r="E144" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3338,7 +3293,7 @@
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3349,7 +3304,7 @@
         <v>149</v>
       </c>
       <c r="E146" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3360,7 +3315,7 @@
         <v>150</v>
       </c>
       <c r="E147" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3371,7 +3326,7 @@
         <v>151</v>
       </c>
       <c r="E148" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3382,7 +3337,7 @@
         <v>152</v>
       </c>
       <c r="E149" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3393,7 +3348,7 @@
         <v>153</v>
       </c>
       <c r="E150" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3404,7 +3359,7 @@
         <v>154</v>
       </c>
       <c r="E151" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3415,7 +3370,7 @@
         <v>155</v>
       </c>
       <c r="E152" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3426,7 +3381,7 @@
         <v>156</v>
       </c>
       <c r="E153" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3437,7 +3392,7 @@
         <v>157</v>
       </c>
       <c r="E154" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3448,7 +3403,7 @@
         <v>158</v>
       </c>
       <c r="E155" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3459,7 +3414,7 @@
         <v>159</v>
       </c>
       <c r="E156" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3470,7 +3425,7 @@
         <v>160</v>
       </c>
       <c r="E157" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3481,7 +3436,7 @@
         <v>161</v>
       </c>
       <c r="E158" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3492,7 +3447,7 @@
         <v>162</v>
       </c>
       <c r="E159" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3503,7 +3458,7 @@
         <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3514,7 +3469,7 @@
         <v>164</v>
       </c>
       <c r="E161" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3525,7 +3480,7 @@
         <v>165</v>
       </c>
       <c r="E162" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3536,7 +3491,7 @@
         <v>166</v>
       </c>
       <c r="E163" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3547,7 +3502,7 @@
         <v>167</v>
       </c>
       <c r="E164" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3558,7 +3513,7 @@
         <v>168</v>
       </c>
       <c r="E165" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3569,7 +3524,7 @@
         <v>169</v>
       </c>
       <c r="E166" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3580,7 +3535,7 @@
         <v>170</v>
       </c>
       <c r="E167" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3591,7 +3546,7 @@
         <v>171</v>
       </c>
       <c r="E168" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3602,7 +3557,7 @@
         <v>172</v>
       </c>
       <c r="E169" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3613,7 +3568,7 @@
         <v>173</v>
       </c>
       <c r="E170" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3624,7 +3579,7 @@
         <v>174</v>
       </c>
       <c r="E171" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3635,7 +3590,7 @@
         <v>175</v>
       </c>
       <c r="E172" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3646,7 +3601,7 @@
         <v>176</v>
       </c>
       <c r="E173" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3657,7 +3612,7 @@
         <v>177</v>
       </c>
       <c r="E174" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3668,7 +3623,7 @@
         <v>178</v>
       </c>
       <c r="E175" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3679,7 +3634,7 @@
         <v>179</v>
       </c>
       <c r="E176" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3690,7 +3645,7 @@
         <v>180</v>
       </c>
       <c r="E177" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3701,7 +3656,7 @@
         <v>181</v>
       </c>
       <c r="E178" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3712,7 +3667,7 @@
         <v>182</v>
       </c>
       <c r="E179" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3723,7 +3678,7 @@
         <v>183</v>
       </c>
       <c r="E180" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3734,7 +3689,7 @@
         <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3745,7 +3700,7 @@
         <v>185</v>
       </c>
       <c r="E182" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3756,7 +3711,7 @@
         <v>186</v>
       </c>
       <c r="E183" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3767,7 +3722,7 @@
         <v>187</v>
       </c>
       <c r="E184" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3778,7 +3733,7 @@
         <v>188</v>
       </c>
       <c r="E185" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3789,7 +3744,7 @@
         <v>189</v>
       </c>
       <c r="E186" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3800,7 +3755,7 @@
         <v>190</v>
       </c>
       <c r="E187" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3811,7 +3766,7 @@
         <v>191</v>
       </c>
       <c r="E188" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3822,7 +3777,7 @@
         <v>192</v>
       </c>
       <c r="E189" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3833,7 +3788,7 @@
         <v>193</v>
       </c>
       <c r="E190" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3844,7 +3799,7 @@
         <v>194</v>
       </c>
       <c r="E191" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3855,7 +3810,7 @@
         <v>195</v>
       </c>
       <c r="E192" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3866,7 +3821,7 @@
         <v>196</v>
       </c>
       <c r="E193" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3877,7 +3832,7 @@
         <v>197</v>
       </c>
       <c r="E194" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3888,7 +3843,7 @@
         <v>198</v>
       </c>
       <c r="E195" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3899,7 +3854,7 @@
         <v>199</v>
       </c>
       <c r="E196" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3910,7 +3865,7 @@
         <v>200</v>
       </c>
       <c r="E197" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3921,7 +3876,7 @@
         <v>201</v>
       </c>
       <c r="E198" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3932,7 +3887,7 @@
         <v>202</v>
       </c>
       <c r="E199" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3943,7 +3898,7 @@
         <v>203</v>
       </c>
       <c r="E200" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3954,7 +3909,7 @@
         <v>204</v>
       </c>
       <c r="E201" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3965,7 +3920,7 @@
         <v>205</v>
       </c>
       <c r="E202" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3976,7 +3931,7 @@
         <v>206</v>
       </c>
       <c r="E203" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3987,7 +3942,7 @@
         <v>207</v>
       </c>
       <c r="E204" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3998,7 +3953,7 @@
         <v>208</v>
       </c>
       <c r="E205" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4009,7 +3964,7 @@
         <v>209</v>
       </c>
       <c r="E206" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4020,7 +3975,7 @@
         <v>210</v>
       </c>
       <c r="E207" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4031,7 +3986,7 @@
         <v>211</v>
       </c>
       <c r="E208" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4042,7 +3997,7 @@
         <v>212</v>
       </c>
       <c r="E209" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4053,7 +4008,7 @@
         <v>213</v>
       </c>
       <c r="E210" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4064,7 +4019,7 @@
         <v>214</v>
       </c>
       <c r="E211" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4075,7 +4030,7 @@
         <v>215</v>
       </c>
       <c r="E212" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4086,7 +4041,7 @@
         <v>216</v>
       </c>
       <c r="E213" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4097,7 +4052,7 @@
         <v>217</v>
       </c>
       <c r="E214" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4108,7 +4063,7 @@
         <v>218</v>
       </c>
       <c r="E215" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4119,7 +4074,7 @@
         <v>219</v>
       </c>
       <c r="E216" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4130,7 +4085,7 @@
         <v>220</v>
       </c>
       <c r="E217" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4141,7 +4096,7 @@
         <v>221</v>
       </c>
       <c r="E218" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4152,7 +4107,7 @@
         <v>222</v>
       </c>
       <c r="E219" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4163,7 +4118,7 @@
         <v>223</v>
       </c>
       <c r="E220" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4174,7 +4129,7 @@
         <v>224</v>
       </c>
       <c r="E221" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4185,7 +4140,7 @@
         <v>225</v>
       </c>
       <c r="E222" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4196,7 +4151,7 @@
         <v>226</v>
       </c>
       <c r="E223" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4207,7 +4162,7 @@
         <v>227</v>
       </c>
       <c r="E224" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4218,7 +4173,7 @@
         <v>228</v>
       </c>
       <c r="E225" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4229,7 +4184,7 @@
         <v>229</v>
       </c>
       <c r="E226" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4240,7 +4195,7 @@
         <v>230</v>
       </c>
       <c r="E227" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4251,7 +4206,7 @@
         <v>231</v>
       </c>
       <c r="E228" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4262,7 +4217,7 @@
         <v>232</v>
       </c>
       <c r="E229" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4273,7 +4228,7 @@
         <v>233</v>
       </c>
       <c r="E230" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4284,7 +4239,7 @@
         <v>234</v>
       </c>
       <c r="E231" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4295,7 +4250,7 @@
         <v>235</v>
       </c>
       <c r="E232" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4306,7 +4261,7 @@
         <v>236</v>
       </c>
       <c r="E233" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4317,7 +4272,7 @@
         <v>237</v>
       </c>
       <c r="E234" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4328,7 +4283,7 @@
         <v>238</v>
       </c>
       <c r="E235" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4339,7 +4294,7 @@
         <v>239</v>
       </c>
       <c r="E236" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4350,7 +4305,7 @@
         <v>240</v>
       </c>
       <c r="E237" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4361,7 +4316,7 @@
         <v>241</v>
       </c>
       <c r="E238" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4372,7 +4327,7 @@
         <v>242</v>
       </c>
       <c r="E239" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4383,7 +4338,7 @@
         <v>243</v>
       </c>
       <c r="E240" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4394,7 +4349,7 @@
         <v>244</v>
       </c>
       <c r="E241" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4405,7 +4360,7 @@
         <v>245</v>
       </c>
       <c r="E242" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4416,7 +4371,7 @@
         <v>246</v>
       </c>
       <c r="E243" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4427,7 +4382,7 @@
         <v>247</v>
       </c>
       <c r="E244" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4438,7 +4393,7 @@
         <v>248</v>
       </c>
       <c r="E245" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4449,7 +4404,7 @@
         <v>249</v>
       </c>
       <c r="E246" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4460,7 +4415,7 @@
         <v>250</v>
       </c>
       <c r="E247" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4471,7 +4426,7 @@
         <v>251</v>
       </c>
       <c r="E248" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4482,7 +4437,7 @@
         <v>252</v>
       </c>
       <c r="E249" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4493,7 +4448,7 @@
         <v>253</v>
       </c>
       <c r="E250" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4504,7 +4459,7 @@
         <v>254</v>
       </c>
       <c r="E251" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4515,7 +4470,7 @@
         <v>255</v>
       </c>
       <c r="E252" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4526,7 +4481,7 @@
         <v>256</v>
       </c>
       <c r="E253" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4537,7 +4492,7 @@
         <v>257</v>
       </c>
       <c r="E254" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4548,7 +4503,7 @@
         <v>258</v>
       </c>
       <c r="E255" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4559,7 +4514,7 @@
         <v>259</v>
       </c>
       <c r="E256" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4570,7 +4525,7 @@
         <v>260</v>
       </c>
       <c r="E257" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4581,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="E258" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4592,7 +4547,7 @@
         <v>262</v>
       </c>
       <c r="E259" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4603,7 +4558,7 @@
         <v>263</v>
       </c>
       <c r="E260" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4614,7 +4569,7 @@
         <v>264</v>
       </c>
       <c r="E261" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4625,7 +4580,7 @@
         <v>265</v>
       </c>
       <c r="E262" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4636,205 +4591,7 @@
         <v>266</v>
       </c>
       <c r="E263" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
-      <c r="A264">
-        <v>1</v>
-      </c>
-      <c r="B264" t="s">
-        <v>267</v>
-      </c>
-      <c r="E264" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
-      <c r="A265">
-        <v>2</v>
-      </c>
-      <c r="B265" t="s">
-        <v>268</v>
-      </c>
-      <c r="E265" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
-      <c r="A266">
-        <v>3</v>
-      </c>
-      <c r="B266" t="s">
-        <v>269</v>
-      </c>
-      <c r="E266" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
-      <c r="A267">
-        <v>4</v>
-      </c>
-      <c r="B267" t="s">
-        <v>270</v>
-      </c>
-      <c r="E267" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
-      <c r="A268">
-        <v>5</v>
-      </c>
-      <c r="B268" t="s">
-        <v>271</v>
-      </c>
-      <c r="E268" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
-      <c r="A269">
-        <v>6</v>
-      </c>
-      <c r="B269" t="s">
-        <v>272</v>
-      </c>
-      <c r="E269" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
-      <c r="A270">
-        <v>7</v>
-      </c>
-      <c r="B270" t="s">
-        <v>273</v>
-      </c>
-      <c r="E270" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
-      <c r="A271">
-        <v>1</v>
-      </c>
-      <c r="B271" t="s">
-        <v>274</v>
-      </c>
-      <c r="E271" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
-      <c r="A272">
-        <v>2</v>
-      </c>
-      <c r="B272" t="s">
-        <v>268</v>
-      </c>
-      <c r="E272" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5">
-      <c r="A273">
-        <v>3</v>
-      </c>
-      <c r="B273" t="s">
-        <v>269</v>
-      </c>
-      <c r="E273" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
-      <c r="A274">
-        <v>4</v>
-      </c>
-      <c r="B274" t="s">
-        <v>270</v>
-      </c>
-      <c r="E274" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
-      <c r="A275">
-        <v>5</v>
-      </c>
-      <c r="B275" t="s">
-        <v>271</v>
-      </c>
-      <c r="E275" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
-      <c r="A276">
-        <v>6</v>
-      </c>
-      <c r="B276" t="s">
-        <v>272</v>
-      </c>
-      <c r="E276" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
-      <c r="A277">
-        <v>7</v>
-      </c>
-      <c r="B277" t="s">
-        <v>273</v>
-      </c>
-      <c r="E277" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
-      <c r="A278">
-        <v>1</v>
-      </c>
-      <c r="B278" t="s">
-        <v>275</v>
-      </c>
-      <c r="E278" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
-      <c r="A279">
-        <v>2</v>
-      </c>
-      <c r="B279" t="s">
-        <v>276</v>
-      </c>
-      <c r="E279" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
-      <c r="A280">
-        <v>3</v>
-      </c>
-      <c r="B280" t="s">
-        <v>277</v>
-      </c>
-      <c r="E280" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
-      <c r="A281">
-        <v>4</v>
-      </c>
-      <c r="B281" t="s">
-        <v>278</v>
-      </c>
-      <c r="E281" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/backend/POC/regulation_chunks.xlsx
+++ b/backend/POC/regulation_chunks.xlsx
@@ -1,20 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B294\Downloads\cv10\backend\POC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0FA620-1E50-4244-8E5F-F02B33E0B84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-51060" yWindow="-1665" windowWidth="20880" windowHeight="19695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="335">
   <si>
     <t>chunk_id</t>
   </si>
@@ -86,53 +108,6 @@
   </si>
   <si>
     <t>Staff supporting merchant accounts must receive adequate and up-to-date compliance training that is sufficient to enable them to perform their duties competently.</t>
-  </si>
-  <si>
-    <t>a:In circumstances where:
-a. your claim arises from an Extraordinary
-Catastrophe;
-b. your claim is fraudulent, or we
-reasonably suspect it is fraudulent;
-c. you do not respond to our reasonable
-inquiries or to our requests for
-document or information about
-your claim;
-d. we have difficulty communicating
-with you about your claim due to
-circumstances beyond our control; or
-e. you request a delay in the claims process;
-then within 12 months of receiving your
-claim we will tell you our decision in
-writing. If we cannot make a decision
-within 12 months, we will tell you in
-writing about our Complaints process.</t>
-  </si>
-  <si>
-    <t>b:If you make a claim, then we will tell you: a. about our claims process; b. about any excess amounts you have to cover or pay in relation to your claim; c. about any waiting or no cover periods that need to finish before we start paying you under the policy; and d. how to contact us regarding your claim.</t>
-  </si>
-  <si>
-    <t>c:We will tell you about the progress of your claim at least every 20 Business Days.</t>
-  </si>
-  <si>
-    <t>d:When we assess your claim, we will consider all relevant facts, the terms of your insurance policy and the law.</t>
-  </si>
-  <si>
-    <t>e:When we receive your Complaint, we will acknowledge that we have received it.</t>
-  </si>
-  <si>
-    <t>f:This part applies to Retail Insurance products only.</t>
-  </si>
-  <si>
-    <t>g:We will not sell you a Consumer Credit Insurance product during the deferred sales period.</t>
-  </si>
-  <si>
-    <t>h:You can take your Complaint to the Australian Financial Complaints Authority at any time and if we do not resolve your Complaint within 30 Calendar Days after we first received your Complaint.</t>
-  </si>
-  <si>
-    <t>i:Words and phrases that have a special meaning in the Code are listed with their meaning in part 16.</t>
-  </si>
-  <si>
-    <t>j:We will require our Employees and Distributors to receive appropriate education and training: a. to provide their services competently; b. to deal with you professionally; and c. about the Code.</t>
   </si>
   <si>
     <t># 2023-COP_UPDATE_October_FINAL.pdf
@@ -1162,6 +1137,190 @@
 8.30am to 5pm Monday to Friday 02 9253 5100 or 1300 728 228 www.insurancecouncil.com.au Published 1 October 2023 All images, content and design are the Copyright of the Insurance Council of Australia 2021.</t>
   </si>
   <si>
+    <t>7All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
+  </si>
+  <si>
+    <t>8The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
+  </si>
+  <si>
+    <t>17Payment service providers shall establish and maintain a real-time transaction monitoring system capable of detecting anomalous or potentially fraudulent activity.</t>
+  </si>
+  <si>
+    <t>10Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
+  </si>
+  <si>
+    <t>9Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
+  </si>
+  <si>
+    <t>13Payment service providers shall implement adequate technical and organizational safeguards to protect consumer data against unauthorized access, disclosure, or destruction.</t>
+  </si>
+  <si>
+    <t>11Verification records shall be retained for a minimum period of seven years from the date of merchant account closure.</t>
+  </si>
+  <si>
+    <t>22If a complaint cannot be resolved within the prescribed timeframe, the provider shall escalate the matter to the Consumer Mediation Office and inform the consumer in writing of the escalation.</t>
+  </si>
+  <si>
+    <t>18Transactions exceeding the threshold amount specified in Annex III must be flagged for manual review and reported to the Financial Intelligence Unit within five business days.</t>
+  </si>
+  <si>
+    <t>20Every payment service provider must establish a formal consumer complaint resolution procedure that is easily accessible and clearly communicated to all users.</t>
+  </si>
+  <si>
+    <t>21Consumer complaints must be acknowledged within two business days and resolved within 30 calendar days of receipt.</t>
+  </si>
+  <si>
+    <t>The process of phone company must be terminated if it takes more than 30 days for any reason</t>
+  </si>
+  <si>
+    <t>After receiving the customer’s personal information, it is necessary to verify the correctness of their personal information</t>
+  </si>
+  <si>
+    <t>When the customer receives the sim card, the phone company must activate the SIM card so that the customer can use the SIM card normally</t>
+  </si>
+  <si>
+    <t>Before retrieving any kind of personal data from the Data Subject, the Data Controller has to ask the Data Subject for consent</t>
+  </si>
+  <si>
+    <t>Customers with outstanding debt exceeding 50 € are not eligible to receive new SIM cardsIf the third party denies portability, the customer’s personal data must be deleted from the database</t>
+  </si>
+  <si>
+    <t>If local anesthesia is administered and the patient has a high tolerance to anesthesia, additional anesthesia must be administered every 20 minutes</t>
+  </si>
+  <si>
+    <t>Before a surgical intervention, the nurse must obtain the patient’s consent. After obtaining consent, the doctor must conduct a ``time out'' procedure</t>
+  </si>
+  <si>
+    <t>If the patient is over 65 or has more than 5 medications, a doctor must approve discharge before the patient is discharged.</t>
+  </si>
+  <si>
+    <t>Physical examination and blood test are required before making a diagnosis</t>
+  </si>
+  <si>
+    <t>Blood samples must be collected from all patients</t>
+  </si>
+  <si>
+    <t>The reporting entity must, as soon as practicable, take reasonable measures to:
+(1)               obtain and verify additional KYC information; or
+(2)               update and verify existing KYC information;
+so that the reporting entity is reasonably satisfied that the customer, beneficial owner or person purporting to act on behalf of the customer is the person that the customer, beneficial owner or person purporting to act on behalf of the customer claims to be.
+Note:       A reporting entity is not required to take any measures that would contravene the tipping off offence in section 123 of the Act.</t>
+  </si>
+  <si>
+    <t>Customer due diligence procedures (however described) that comply with one or more laws of a foreign country giving effect to the FATF Recommendations relating to customer due diligence and record-keeping and require the other person to:
+(1)     identify the customer and verify the customer's identity using reliable and independent sources, so that the other person is satisfied that it knows who the customer is; and
+(2)     identify the beneficial owner of the customer and take reasonable measures to verify the identity of the beneficial owner, so that the other person is satisfied that it knows who the beneficial owner is; and
+(3)     identify a person acting on behalf of the customer and take reasonable steps to verify the person's identity and authority to act on behalf of the customer, so that the other person is satisfied that it knows who the person is and that the person has authority to act on behalf of the customer.
+Note 1:       Country has meaning given by section 5 of the Act.
+Note 2:       A foreign country may include a region or regions. These regions may have a different risk profile to each other or the rest of the foreign country.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls that are designed to enable the reporting entity to be reasonably satisfied, where a customer is an individual, that the customer is the individual that he or she claims to be.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include a procedure for the reporting entity to collect, at a minimum, the following KYC information about an individual (other than an individual who notifies the reporting entity that he or she is a customer of the reporting entity in his or her capacity as a sole trader):
+(1)      the customer's full name;
+(2)      the customer's date of birth; and
+(3)      the customer's residential address.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include a procedure for the reporting entity to collect at a minimum, the following KYC information about a customer who notifies the reporting entity that he or she is a customer of the reporting entity in his or her capacity as a sole trader:
+(1)      the customer's full name;
+(2)      the customer's date of birth;
+(3)      the full business name (if any) under which the customer carries on his or her business;
+(4)      the full address of the customer's principal place of business (if any) or the customer's residential address; and
+(5)      any ABN issued to the customer.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine whether, in addition to the KYC information referred to in paragraph 4.2.3 or 4.2.4 above, any other KYC information will be collected about a customer.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include a procedure for the reporting entity to verify, at a minimum, the following KYC information about a customer:
+(1)      the customer's full name; and
+(2)      either:
+(a)  the customer's date of birth; or
+(b)  the customer's residential address.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must require that the verification of information collected about a customer be based on:
+(1)      reliable and independent documentation;
+(2)      reliable and independent electronic data; or
+(3)      a combination of (1) and (2) above.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine whether, in addition to the KYC information referred to in paragraph 4.2.6 above, any other KYC information collected about the customer should be verified from reliable and independent documentation, reliable and independent electronic data or a combination of the two.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to respond to any discrepancy that arises in the course of verifying KYC information collected about a customer so that the reporting entity can determine whether it is reasonably satisfied that the customer is the person that he or she claims to be.</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must require that the reporting entity be satisfied that any document from which the reporting entity verifies KYC information about an individual has not expired (other than in the case of a passport issued by the Commonwealth that expired within the preceding two years).</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine:
+(1)      whether the electronic data is reliable and independent, taking into account the following factors:
+(a)    the accuracy of the data;
+(b)    how secure the data is;
+(c)    how the data is kept up‑to‑date;
+(d)   how comprehensive the data is (for example, by reference to the range of persons included in the data and the period over which the data has been collected);
+(e)    whether the data has been verified from a reliable and independent source;
+(f)    whether the data is maintained by a government body or pursuant to legislation; and
+(g)    whether the electronic data can be additionally authenticated; and
+(2)      what reliable and independent electronic data the reporting entity will use for the purpose of verification;
+(3)      the reporting entity's pre‑defined tolerance levels for matches and errors; and
+(4)      whether, and how, to confirm KYC information collected about a customer by independently initiating contact with the person that the customer claims to be.</t>
+  </si>
+  <si>
+    <t>A reporting entity must apply appropriate levels of ongoing customer due diligence in order to identify, mitigate and manage any ML/TF risk associated with customer identities established using self-attestation.</t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity is an organisation, the entity must not collect personal information (other than sensitive information) unless the information is reasonably necessary for one or more of the entity's functions or activities.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must not collect sensitive information about an individual unless:
+a) the individual consents to the collection of the information and:
+- if the entity is an agency — the information is reasonably necessary for, or directly related to, one or more of the entity's functions or activities; or
+- if the entity is an organisation — the information is reasonably necessary for one or more of the entity's functions or activities; or
+b) subclause 3.4 Australian Privacy Principlelies in relation to the information.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must collect personal information only by lawful and fair means.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must collect personal information about an individual only from the individual unless:
+a) if the entity is an agency:
+- the individual consents to the collection of the information from someone other than the individual; or
+- the entity is required or authorised by or under an Australian law, or a court/tribunal order, to collect the information from someone other than the individual; or
+b) it is unreasonable or impracticable to do so.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must take such steps (if any) as are reasonable in the circumstances to ensure that the personal information that the entity collects is accurate, up-to-date and complete.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must take such steps (if any) as are reasonable in the circumstances to ensure that the personal information that the entity uses or discloses is, having regard to the purpose of the use or disclosure, accurate, up-to-date, complete and relevant.</t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity holds personal information, the entity must take such steps as are reasonable in the circumstances to protect the information:
+a) from misuse, interference and loss; and
+b) from unauthorised access, modification or disclosure.</t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity holds personal information about an individual, the entity must, on request by the individual, give the individual access to the information.</t>
+  </si>
+  <si>
+    <t>At or before the time or, if that is not practicable, as soon as practicable after, an Australian Privacy Principle entity collects personal information about an individual, the entity must take such steps (if any) as are reasonable in the circumstances:
+a) to notify the individual of such matters referred to in subclause 5.2 as are reasonable in the circumstances; or
+b) to otherwise ensure that the individual is aware of any such matters.</t>
+  </si>
+  <si>
+    <t>If:
+a) an Australian Privacy Principle entity holds personal information about an individual; and
+b) the entity no longer needs the information for any purpose for which the information may be used or disclosed by the entity under this Schedule; and
+c) the information is not contained in a Commonwealth record; and
+d) the entity is not required by or under an Australian law, or a court/tribunal order, to retain the information;
+the entity must take such steps as are reasonable in the circumstances to destroy the information or to ensure that the information is de-identified.</t>
+  </si>
+  <si>
     <t>obligation</t>
   </si>
   <si>
@@ -1174,9 +1333,6 @@
     <t>conditional</t>
   </si>
   <si>
-    <t>timeframe</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -1186,18 +1342,163 @@
     <t>Synthetic Compliance Rules #1</t>
   </si>
   <si>
-    <t>Insurance Compliance Rules</t>
-  </si>
-  <si>
     <t>TravelTest</t>
+  </si>
+  <si>
+    <t>barrientos_sim_card</t>
+  </si>
+  <si>
+    <t>barritentos_emergencies</t>
+  </si>
+  <si>
+    <t>sai_bank_account_opening_process</t>
+  </si>
+  <si>
+    <t>claude_merchant_onboarding</t>
+  </si>
+  <si>
+    <t>Rejection communications must acknowledge the candidate's application in sufficient detail to demonstrate due consideration.</t>
+  </si>
+  <si>
+    <t>For each year of service with an employer (other than periods of employment as a casual employee of the employer), an employee is entitled to:
+                     (a)  4 weeks of paid annual leave; or
+                     (b)  5 weeks of paid annual leave, if:
+                              (i)  a modern award applies to the employee and defines or describes the employee as a shiftworker for the purposes of the National Employment Standards; or
+                             (ii)  an enterprise agreement applies to the employee and defines or describes the employee as a shiftworker for the purposes of the National Employment Standards; or
+                            (iii)  the employee qualifies for the shiftworker annual leave entitlement under subsection (3) (this relates to award/agreement free employees).
+Note:          Section 196 affects whether the FWC may approve an enterprise agreement covering an employee, if the employee is covered by a modern award that is in operation and defines or describes the employee as a shiftworker for the purposes of the National Employment Standards.
+Accrual of leave</t>
+  </si>
+  <si>
+    <t>A person who causes, instructs, induces, aids or permits another person to do an act that is unlawful under Division 1, 2, 2A, 3 or 6 of Part 2 is, for the purposes of this Act, taken also to have done the act.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An employer must not request or require an employee to work more than the following number of hours in a week unless the additional hours are reasonable:
+    (a)  for a full‑time employee—38 hours; or
+    (b)  for an employee who is not a full‑time employee—the lesser of:
+    (i)  38 hours; and
+    (ii)  the employee’s ordinary hours of work in a week.
+    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A modern award or enterprise agreement may include terms providing for the averaging of hours of work over a specified period. The average weekly hours over the period must not exceed:
+                     (a)  for a full‑time employee—38 hours; or
+                     (b)  for an employee who is not a full‑time employee—the lesser of:
+                              (i)  38 hours; and
+                             (ii)  the employee’s ordinary hours of work in a week.
+    </t>
+  </si>
+  <si>
+    <t>A person must not make an unlawful termination application in relation to conduct if the person is entitled to make a general protections court application in relation to the conduct.</t>
+  </si>
+  <si>
+    <t>A person who has been dismissed must not make an application or complaint of a kind referred to in any one of sections 726 to 732 in relation to the dismissal if any other of those sections applies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Commission may, by writing under its seal, delegate to:
+                     (a)  a member of the Commission; or
+                     (b)  the Commissioner; or
+                     (c)  a member of the staff of the Commission; or
+                     (d)  another person or body of persons;
+all or any of the powers conferred on the Commission under this Act, other than powers in connection with the performance of the functions that, under section 67, are to be performed by the Commissioner on behalf of the Commission. </t>
+  </si>
+  <si>
+    <t>Hiring entities are prohibited from gathering, recording, or factoring into any decision-making criteria any information pertaining to a candidate's circumstances outside of their professional qualifications. This includes, but is not limited to, health status, economic standing, or any personal situation not directly relevant to the duties of the role. Should such information become relevant, it may only be sought after a conditional offer has been extended, and exclusively for the lawful purpose of facilitating workplace accommodations in accordance with applicable accessibility standards.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Prior to contacting any provided reference, the employer must issue a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>72-hour written notice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the candidate, specifying the name of the reference to be contacted, the method of contact, and the scope of inquiry. Reference checks conducted without this notice period are inadmissible and constitute an unfair labor practice.</t>
+    </r>
+  </si>
+  <si>
+    <t>sai_internal_hiring_process</t>
+  </si>
+  <si>
+    <t>sai_travel_insurance_claims_process</t>
+  </si>
+  <si>
+    <t>a:In circumstances where:
+a. your claim arises from an Extraordinary
+Catastrophe;
+b. your claim is fraudulent, or we
+reasonably suspect it is fraudulent;
+c. you do not respond to our reasonable
+inquiries or to our requests for
+document or information about
+your claim;
+d. we have difficulty communicating
+with you about your claim due to
+circumstances beyond our control; or
+e. you request a delay in the claims process;
+then within 12 months of receiving your
+claim we will tell you our decision in
+writing. If we cannot make a decision
+within 12 months, we will tell you in
+writing about our Complaints process.</t>
+  </si>
+  <si>
+    <t>b:If you make a claim, then we will tell you: a. about our claims process; b. about any excess amounts you have to cover or pay in relation to your claim; c. about any waiting or no cover periods that need to finish before we start paying you under the policy; and d. how to contact us regarding your claim.</t>
+  </si>
+  <si>
+    <t>c:We will tell you about the progress of your claim at least every 20 Business Days.</t>
+  </si>
+  <si>
+    <t>d:When we assess your claim, we will consider all relevant facts, the terms of your insurance policy and the law.</t>
+  </si>
+  <si>
+    <t>e:When we receive your Complaint, we will acknowledge that we have received it.</t>
+  </si>
+  <si>
+    <t>j:We will require our Employees and Distributors to receive appropriate education and training: a. to provide their services competently; b. to deal with you professionally; and c. about the Code.</t>
+  </si>
+  <si>
+    <t>g:We will not sell you a Consumer Credit Insurance product during the deferred sales period.</t>
+  </si>
+  <si>
+    <t>h:You can take your Complaint to the Australian Financial Complaints Authority at any time and if we do not resolve your Complaint within 30 Calendar Days after we first received your Complaint.</t>
+  </si>
+  <si>
+    <t>k:With effect from 1 January 2025, all travel insurance claims shall be submitted exclusively through the FCPA Portal</t>
+  </si>
+  <si>
+    <t>l:Following successful claim registration, the insurer must send a formal written acknowledgement to the policyholder no later than 2 Business Days after the date of registration.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1233,13 +1534,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1277,7 +1586,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1311,6 +1620,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1345,9 +1655,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1520,11 +1831,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E263"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E317"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="59.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1541,7 +1855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>7</v>
       </c>
@@ -1549,16 +1863,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>8</v>
       </c>
@@ -1566,16 +1880,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>9</v>
       </c>
@@ -1583,16 +1897,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1600,16 +1914,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1617,16 +1931,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D6" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>12</v>
       </c>
@@ -1634,16 +1948,16 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>13</v>
       </c>
@@ -1651,16 +1965,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -1668,16 +1982,16 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>15</v>
       </c>
@@ -1685,16 +1999,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>16</v>
       </c>
@@ -1702,16 +2016,16 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>17</v>
       </c>
@@ -1719,16 +2033,16 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>18</v>
       </c>
@@ -1736,16 +2050,16 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>19</v>
       </c>
@@ -1753,16 +2067,16 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="E14" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>20</v>
       </c>
@@ -1770,16 +2084,16 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E15" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>21</v>
       </c>
@@ -1787,16 +2101,16 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E16" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>22</v>
       </c>
@@ -1804,16 +2118,16 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>27</v>
       </c>
@@ -1821,16 +2135,16 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="D18" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>28</v>
       </c>
@@ -1838,16 +2152,16 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D19" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>29</v>
       </c>
@@ -1855,2746 +2169,3284 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D20" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
-        <v>267</v>
-      </c>
-      <c r="D21" t="s">
-        <v>272</v>
-      </c>
       <c r="E21" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
-        <v>267</v>
-      </c>
-      <c r="D22" t="s">
-        <v>272</v>
-      </c>
       <c r="E22" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>271</v>
-      </c>
-      <c r="D23" t="s">
-        <v>272</v>
-      </c>
       <c r="E23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
-      <c r="C24" t="s">
-        <v>267</v>
-      </c>
-      <c r="D24" t="s">
-        <v>273</v>
-      </c>
       <c r="E24" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5</v>
       </c>
       <c r="B25" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25" t="s">
-        <v>273</v>
-      </c>
       <c r="E25" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="D26" t="s">
-        <v>273</v>
-      </c>
       <c r="E26" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>268</v>
-      </c>
-      <c r="D27" t="s">
-        <v>272</v>
-      </c>
       <c r="E27" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>8</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
-      <c r="C28" t="s">
-        <v>271</v>
-      </c>
-      <c r="D28" t="s">
-        <v>272</v>
-      </c>
       <c r="E28" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>9</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
       </c>
-      <c r="C29" t="s">
-        <v>269</v>
-      </c>
-      <c r="D29" t="s">
-        <v>273</v>
-      </c>
       <c r="E29" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
       </c>
-      <c r="C30" t="s">
-        <v>267</v>
-      </c>
-      <c r="D30" t="s">
-        <v>272</v>
-      </c>
       <c r="E30" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
         <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
         <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
       </c>
       <c r="E55" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
       </c>
       <c r="E60" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
         <v>65</v>
       </c>
       <c r="E62" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
       </c>
       <c r="E66" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
         <v>70</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
       </c>
       <c r="E68" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
       </c>
       <c r="E69" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B70" t="s">
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
       </c>
       <c r="E71" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B72" t="s">
         <v>75</v>
       </c>
       <c r="E72" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
         <v>76</v>
       </c>
       <c r="E73" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B74" t="s">
         <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
         <v>78</v>
       </c>
       <c r="E75" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B76" t="s">
         <v>79</v>
       </c>
       <c r="E76" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B78" t="s">
         <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
         <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
         <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B81" t="s">
         <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
         <v>85</v>
       </c>
       <c r="E82" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B83" t="s">
         <v>86</v>
       </c>
       <c r="E83" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B84" t="s">
         <v>87</v>
       </c>
       <c r="E84" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
         <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B86" t="s">
         <v>89</v>
       </c>
       <c r="E86" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s">
         <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
         <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
         <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
       </c>
       <c r="E90" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B91" t="s">
         <v>94</v>
       </c>
       <c r="E91" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s">
         <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B93" t="s">
         <v>96</v>
       </c>
       <c r="E93" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B94" t="s">
         <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
       </c>
       <c r="E95" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s">
         <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B97" t="s">
         <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B98" t="s">
         <v>101</v>
       </c>
       <c r="E98" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
       </c>
       <c r="E99" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B100" t="s">
         <v>103</v>
       </c>
       <c r="E100" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B101" t="s">
         <v>104</v>
       </c>
       <c r="E101" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s">
         <v>105</v>
       </c>
       <c r="E102" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B103" t="s">
         <v>106</v>
       </c>
       <c r="E103" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B104" t="s">
         <v>107</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s">
         <v>108</v>
       </c>
       <c r="E105" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B106" t="s">
         <v>109</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B107" t="s">
         <v>110</v>
       </c>
       <c r="E107" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B108" t="s">
         <v>111</v>
       </c>
       <c r="E108" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B109" t="s">
         <v>112</v>
       </c>
       <c r="E109" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B110" t="s">
         <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B112" t="s">
         <v>115</v>
       </c>
       <c r="E112" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B113" t="s">
         <v>116</v>
       </c>
       <c r="E113" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B114" t="s">
         <v>117</v>
       </c>
       <c r="E114" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B115" t="s">
         <v>118</v>
       </c>
       <c r="E115" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B116" t="s">
         <v>119</v>
       </c>
       <c r="E116" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B117" t="s">
         <v>120</v>
       </c>
       <c r="E117" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B118" t="s">
         <v>121</v>
       </c>
       <c r="E118" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B119" t="s">
         <v>122</v>
       </c>
       <c r="E119" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B120" t="s">
         <v>123</v>
       </c>
       <c r="E120" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B121" t="s">
         <v>124</v>
       </c>
       <c r="E121" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B122" t="s">
         <v>125</v>
       </c>
       <c r="E122" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B123" t="s">
         <v>126</v>
       </c>
       <c r="E123" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B124" t="s">
         <v>127</v>
       </c>
       <c r="E124" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B125" t="s">
         <v>128</v>
       </c>
       <c r="E125" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B126" t="s">
         <v>129</v>
       </c>
       <c r="E126" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B127" t="s">
         <v>130</v>
       </c>
       <c r="E127" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B128" t="s">
         <v>131</v>
       </c>
       <c r="E128" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B129" t="s">
         <v>132</v>
       </c>
       <c r="E129" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B130" t="s">
         <v>133</v>
       </c>
       <c r="E130" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B131" t="s">
         <v>134</v>
       </c>
       <c r="E131" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B132" t="s">
         <v>135</v>
       </c>
       <c r="E132" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B133" t="s">
         <v>136</v>
       </c>
       <c r="E133" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B134" t="s">
         <v>137</v>
       </c>
       <c r="E134" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B135" t="s">
         <v>138</v>
       </c>
       <c r="E135" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B136" t="s">
         <v>139</v>
       </c>
       <c r="E136" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B137" t="s">
         <v>140</v>
       </c>
       <c r="E137" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B138" t="s">
         <v>141</v>
       </c>
       <c r="E138" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B139" t="s">
         <v>142</v>
       </c>
       <c r="E139" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B140" t="s">
         <v>143</v>
       </c>
       <c r="E140" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B141" t="s">
         <v>144</v>
       </c>
       <c r="E141" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B142" t="s">
         <v>145</v>
       </c>
       <c r="E142" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B143" t="s">
         <v>146</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B144" t="s">
         <v>147</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B145" t="s">
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B146" t="s">
         <v>149</v>
       </c>
       <c r="E146" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B147" t="s">
         <v>150</v>
       </c>
       <c r="E147" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B148" t="s">
         <v>151</v>
       </c>
       <c r="E148" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B149" t="s">
         <v>152</v>
       </c>
       <c r="E149" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B150" t="s">
         <v>153</v>
       </c>
       <c r="E150" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B151" t="s">
         <v>154</v>
       </c>
       <c r="E151" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B152" t="s">
         <v>155</v>
       </c>
       <c r="E152" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B153" t="s">
         <v>156</v>
       </c>
       <c r="E153" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B154" t="s">
         <v>157</v>
       </c>
       <c r="E154" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B155" t="s">
         <v>158</v>
       </c>
       <c r="E155" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B156" t="s">
         <v>159</v>
       </c>
       <c r="E156" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B157" t="s">
         <v>160</v>
       </c>
       <c r="E157" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B158" t="s">
         <v>161</v>
       </c>
       <c r="E158" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B159" t="s">
         <v>162</v>
       </c>
       <c r="E159" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B160" t="s">
         <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B161" t="s">
         <v>164</v>
       </c>
       <c r="E161" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B162" t="s">
         <v>165</v>
       </c>
       <c r="E162" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B163" t="s">
         <v>166</v>
       </c>
       <c r="E163" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B164" t="s">
         <v>167</v>
       </c>
       <c r="E164" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B165" t="s">
         <v>168</v>
       </c>
       <c r="E165" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B166" t="s">
         <v>169</v>
       </c>
       <c r="E166" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B167" t="s">
         <v>170</v>
       </c>
       <c r="E167" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B168" t="s">
         <v>171</v>
       </c>
       <c r="E168" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B169" t="s">
         <v>172</v>
       </c>
       <c r="E169" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B170" t="s">
         <v>173</v>
       </c>
       <c r="E170" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B171" t="s">
         <v>174</v>
       </c>
       <c r="E171" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B172" t="s">
         <v>175</v>
       </c>
       <c r="E172" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B173" t="s">
         <v>176</v>
       </c>
       <c r="E173" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B174" t="s">
         <v>177</v>
       </c>
       <c r="E174" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B175" t="s">
         <v>178</v>
       </c>
       <c r="E175" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B176" t="s">
         <v>179</v>
       </c>
       <c r="E176" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B177" t="s">
         <v>180</v>
       </c>
       <c r="E177" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B178" t="s">
         <v>181</v>
       </c>
       <c r="E178" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B179" t="s">
         <v>182</v>
       </c>
       <c r="E179" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B180" t="s">
         <v>183</v>
       </c>
       <c r="E180" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B181" t="s">
         <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B182" t="s">
         <v>185</v>
       </c>
       <c r="E182" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B183" t="s">
         <v>186</v>
       </c>
       <c r="E183" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B184" t="s">
         <v>187</v>
       </c>
       <c r="E184" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B185" t="s">
         <v>188</v>
       </c>
       <c r="E185" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B186" t="s">
         <v>189</v>
       </c>
       <c r="E186" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B187" t="s">
         <v>190</v>
       </c>
       <c r="E187" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B188" t="s">
         <v>191</v>
       </c>
       <c r="E188" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B189" t="s">
         <v>192</v>
       </c>
       <c r="E189" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B190" t="s">
         <v>193</v>
       </c>
       <c r="E190" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B191" t="s">
         <v>194</v>
       </c>
       <c r="E191" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B192" t="s">
         <v>195</v>
       </c>
       <c r="E192" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B193" t="s">
         <v>196</v>
       </c>
       <c r="E193" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B194" t="s">
         <v>197</v>
       </c>
       <c r="E194" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B195" t="s">
         <v>198</v>
       </c>
       <c r="E195" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B196" t="s">
         <v>199</v>
       </c>
       <c r="E196" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B197" t="s">
         <v>200</v>
       </c>
       <c r="E197" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B198" t="s">
         <v>201</v>
       </c>
       <c r="E198" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B199" t="s">
         <v>202</v>
       </c>
       <c r="E199" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B200" t="s">
         <v>203</v>
       </c>
       <c r="E200" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B201" t="s">
         <v>204</v>
       </c>
       <c r="E201" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B202" t="s">
         <v>205</v>
       </c>
       <c r="E202" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B203" t="s">
         <v>206</v>
       </c>
       <c r="E203" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B204" t="s">
         <v>207</v>
       </c>
       <c r="E204" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B205" t="s">
         <v>208</v>
       </c>
       <c r="E205" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B206" t="s">
         <v>209</v>
       </c>
       <c r="E206" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B207" t="s">
         <v>210</v>
       </c>
       <c r="E207" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B208" t="s">
         <v>211</v>
       </c>
       <c r="E208" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B209" t="s">
         <v>212</v>
       </c>
       <c r="E209" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B210" t="s">
         <v>213</v>
       </c>
       <c r="E210" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B211" t="s">
         <v>214</v>
       </c>
       <c r="E211" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B212" t="s">
         <v>215</v>
       </c>
       <c r="E212" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B213" t="s">
         <v>216</v>
       </c>
       <c r="E213" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B214" t="s">
         <v>217</v>
       </c>
       <c r="E214" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B215" t="s">
         <v>218</v>
       </c>
       <c r="E215" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B216" t="s">
         <v>219</v>
       </c>
       <c r="E216" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B217" t="s">
         <v>220</v>
       </c>
       <c r="E217" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B218" t="s">
         <v>221</v>
       </c>
       <c r="E218" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B219" t="s">
         <v>222</v>
       </c>
       <c r="E219" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B220" t="s">
         <v>223</v>
       </c>
       <c r="E220" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B221" t="s">
         <v>224</v>
       </c>
       <c r="E221" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B222" t="s">
         <v>225</v>
       </c>
       <c r="E222" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B223" t="s">
         <v>226</v>
       </c>
       <c r="E223" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B224" t="s">
         <v>227</v>
       </c>
       <c r="E224" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B225" t="s">
         <v>228</v>
       </c>
       <c r="E225" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B226" t="s">
         <v>229</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B227" t="s">
         <v>230</v>
       </c>
       <c r="E227" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B228" t="s">
         <v>231</v>
       </c>
       <c r="E228" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B229" t="s">
         <v>232</v>
       </c>
       <c r="E229" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B230" t="s">
         <v>233</v>
       </c>
       <c r="E230" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B231" t="s">
         <v>234</v>
       </c>
       <c r="E231" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B232" t="s">
         <v>235</v>
       </c>
       <c r="E232" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B233" t="s">
         <v>236</v>
       </c>
       <c r="E233" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B234" t="s">
         <v>237</v>
       </c>
       <c r="E234" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B235" t="s">
         <v>238</v>
       </c>
       <c r="E235" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B236" t="s">
         <v>239</v>
       </c>
       <c r="E236" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B237" t="s">
         <v>240</v>
       </c>
       <c r="E237" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B238" t="s">
         <v>241</v>
       </c>
       <c r="E238" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B239" t="s">
         <v>242</v>
       </c>
       <c r="E239" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B240" t="s">
         <v>243</v>
       </c>
       <c r="E240" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B241" t="s">
         <v>244</v>
       </c>
       <c r="E241" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B242" t="s">
         <v>245</v>
       </c>
       <c r="E242" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="B243" t="s">
         <v>246</v>
       </c>
       <c r="E243" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B244" t="s">
         <v>247</v>
       </c>
       <c r="E244" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B245" t="s">
         <v>248</v>
       </c>
       <c r="E245" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B246" t="s">
         <v>249</v>
       </c>
       <c r="E246" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B247" t="s">
         <v>250</v>
       </c>
       <c r="E247" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B248" t="s">
         <v>251</v>
       </c>
       <c r="E248" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B249" t="s">
         <v>252</v>
       </c>
       <c r="E249" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B250" t="s">
         <v>253</v>
       </c>
       <c r="E250" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B251" t="s">
         <v>254</v>
       </c>
       <c r="E251" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B252" t="s">
         <v>255</v>
       </c>
       <c r="E252" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B253" t="s">
         <v>256</v>
       </c>
       <c r="E253" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="B254" t="s">
         <v>257</v>
       </c>
       <c r="E254" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="B255" t="s">
         <v>258</v>
       </c>
       <c r="E255" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="B256" t="s">
         <v>259</v>
       </c>
       <c r="E256" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>227</v>
+        <v>4</v>
       </c>
       <c r="B257" t="s">
         <v>260</v>
       </c>
       <c r="E257" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>228</v>
+        <v>5</v>
       </c>
       <c r="B258" t="s">
         <v>261</v>
       </c>
       <c r="E258" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>229</v>
+        <v>6</v>
       </c>
       <c r="B259" t="s">
         <v>262</v>
       </c>
       <c r="E259" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="B260" t="s">
         <v>263</v>
       </c>
       <c r="E260" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="B261" t="s">
         <v>264</v>
       </c>
       <c r="E261" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="B262" t="s">
         <v>265</v>
       </c>
       <c r="E262" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>233</v>
+        <v>10</v>
       </c>
       <c r="B263" t="s">
         <v>266</v>
       </c>
       <c r="E263" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>11</v>
+      </c>
+      <c r="B264" t="s">
+        <v>267</v>
+      </c>
+      <c r="E264" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
+        <v>268</v>
+      </c>
+      <c r="E265" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>2</v>
+      </c>
+      <c r="B266" t="s">
+        <v>269</v>
+      </c>
+      <c r="E266" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>3</v>
+      </c>
+      <c r="B267" t="s">
+        <v>270</v>
+      </c>
+      <c r="E267" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>4</v>
+      </c>
+      <c r="B268" t="s">
+        <v>271</v>
+      </c>
+      <c r="E268" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>5</v>
+      </c>
+      <c r="B269" t="s">
+        <v>272</v>
+      </c>
+      <c r="E269" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>1</v>
+      </c>
+      <c r="B270" t="s">
+        <v>273</v>
+      </c>
+      <c r="E270" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>2</v>
+      </c>
+      <c r="B271" t="s">
+        <v>274</v>
+      </c>
+      <c r="E271" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>3</v>
+      </c>
+      <c r="B272" t="s">
+        <v>275</v>
+      </c>
+      <c r="E272" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>4</v>
+      </c>
+      <c r="B273" t="s">
         <v>276</v>
       </c>
+      <c r="E273" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>5</v>
+      </c>
+      <c r="B274" t="s">
+        <v>277</v>
+      </c>
+      <c r="E274" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275" t="s">
+        <v>278</v>
+      </c>
+      <c r="E275" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>2</v>
+      </c>
+      <c r="B276" t="s">
+        <v>279</v>
+      </c>
+      <c r="E276" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>3</v>
+      </c>
+      <c r="B277" t="s">
+        <v>280</v>
+      </c>
+      <c r="E277" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>4</v>
+      </c>
+      <c r="B278" t="s">
+        <v>281</v>
+      </c>
+      <c r="E278" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>5</v>
+      </c>
+      <c r="B279" t="s">
+        <v>282</v>
+      </c>
+      <c r="E279" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>6</v>
+      </c>
+      <c r="B280" t="s">
+        <v>283</v>
+      </c>
+      <c r="E280" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>7</v>
+      </c>
+      <c r="B281" t="s">
+        <v>284</v>
+      </c>
+      <c r="E281" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>8</v>
+      </c>
+      <c r="B282" t="s">
+        <v>285</v>
+      </c>
+      <c r="E282" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>9</v>
+      </c>
+      <c r="B283" t="s">
+        <v>286</v>
+      </c>
+      <c r="E283" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>10</v>
+      </c>
+      <c r="B284" t="s">
+        <v>287</v>
+      </c>
+      <c r="E284" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>11</v>
+      </c>
+      <c r="B285" t="s">
+        <v>288</v>
+      </c>
+      <c r="E285" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>12</v>
+      </c>
+      <c r="B286" t="s">
+        <v>289</v>
+      </c>
+      <c r="E286" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>13</v>
+      </c>
+      <c r="B287" t="s">
+        <v>290</v>
+      </c>
+      <c r="E287" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>14</v>
+      </c>
+      <c r="B288" t="s">
+        <v>291</v>
+      </c>
+      <c r="E288" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>15</v>
+      </c>
+      <c r="B289" t="s">
+        <v>292</v>
+      </c>
+      <c r="E289" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>16</v>
+      </c>
+      <c r="B290" t="s">
+        <v>293</v>
+      </c>
+      <c r="E290" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>17</v>
+      </c>
+      <c r="B291" t="s">
+        <v>294</v>
+      </c>
+      <c r="E291" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>18</v>
+      </c>
+      <c r="B292" t="s">
+        <v>295</v>
+      </c>
+      <c r="E292" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>19</v>
+      </c>
+      <c r="B293" t="s">
+        <v>296</v>
+      </c>
+      <c r="E293" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>20</v>
+      </c>
+      <c r="B294" t="s">
+        <v>297</v>
+      </c>
+      <c r="E294" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>21</v>
+      </c>
+      <c r="B295" t="s">
+        <v>298</v>
+      </c>
+      <c r="E295" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>22</v>
+      </c>
+      <c r="B296" t="s">
+        <v>299</v>
+      </c>
+      <c r="E296" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>23</v>
+      </c>
+      <c r="B297" t="s">
+        <v>300</v>
+      </c>
+      <c r="E297" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>1</v>
+      </c>
+      <c r="B298" t="s">
+        <v>313</v>
+      </c>
+      <c r="E298" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>2</v>
+      </c>
+      <c r="B299" t="s">
+        <v>314</v>
+      </c>
+      <c r="E299" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>3</v>
+      </c>
+      <c r="B300" t="s">
+        <v>315</v>
+      </c>
+      <c r="E300" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>4</v>
+      </c>
+      <c r="B301" t="s">
+        <v>316</v>
+      </c>
+      <c r="E301" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>5</v>
+      </c>
+      <c r="B302" t="s">
+        <v>317</v>
+      </c>
+      <c r="E302" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>6</v>
+      </c>
+      <c r="B303" t="s">
+        <v>318</v>
+      </c>
+      <c r="E303" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>7</v>
+      </c>
+      <c r="B304" t="s">
+        <v>319</v>
+      </c>
+      <c r="E304" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>8</v>
+      </c>
+      <c r="B305" t="s">
+        <v>320</v>
+      </c>
+      <c r="E305" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>9</v>
+      </c>
+      <c r="B306" t="s">
+        <v>321</v>
+      </c>
+      <c r="E306" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>10</v>
+      </c>
+      <c r="B307" t="s">
+        <v>322</v>
+      </c>
+      <c r="E307" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>1</v>
+      </c>
+      <c r="B308" t="s">
+        <v>325</v>
+      </c>
+      <c r="E308" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>2</v>
+      </c>
+      <c r="B309" t="s">
+        <v>326</v>
+      </c>
+      <c r="E309" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>3</v>
+      </c>
+      <c r="B310" t="s">
+        <v>327</v>
+      </c>
+      <c r="E310" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>4</v>
+      </c>
+      <c r="B311" t="s">
+        <v>328</v>
+      </c>
+      <c r="E311" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>5</v>
+      </c>
+      <c r="B312" t="s">
+        <v>329</v>
+      </c>
+      <c r="E312" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>6</v>
+      </c>
+      <c r="B313" t="s">
+        <v>330</v>
+      </c>
+      <c r="E313" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>7</v>
+      </c>
+      <c r="B314" t="s">
+        <v>331</v>
+      </c>
+      <c r="E314" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>8</v>
+      </c>
+      <c r="B315" t="s">
+        <v>332</v>
+      </c>
+      <c r="E315" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>9</v>
+      </c>
+      <c r="B316" t="s">
+        <v>333</v>
+      </c>
+      <c r="E316" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>10</v>
+      </c>
+      <c r="B317" t="s">
+        <v>334</v>
+      </c>
+      <c r="E317" t="s">
+        <v>324</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>